--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA60"/>
+  <dimension ref="A1:BA58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2873.52</v>
+        <v>2802.4</v>
       </c>
       <c r="C2" t="n">
-        <v>2869.48</v>
+        <v>2798.52</v>
       </c>
       <c r="D2" t="n">
-        <v>115.9443522868255</v>
+        <v>115.6325486328488</v>
       </c>
       <c r="E2" t="n">
-        <v>114.167026778371</v>
+        <v>114.1674885296514</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5466933867735471</v>
+        <v>0.5452674897119342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1567806136334055</v>
+        <v>0.1580512073777454</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3758339510748703</v>
+        <v>0.3765243902439024</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2400801603206413</v>
+        <v>0.2411522633744856</v>
       </c>
       <c r="J2" t="n">
-        <v>382</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>514</v>
+        <v>30</v>
       </c>
       <c r="L2" t="n">
-        <v>389</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="N2" t="n">
-        <v>1112</v>
+        <v>1089</v>
       </c>
       <c r="O2" t="n">
-        <v>1337</v>
+        <v>1307</v>
       </c>
       <c r="P2" t="n">
-        <v>0.535871743486974</v>
+        <v>0.5378600823045268</v>
       </c>
       <c r="Q2" t="n">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="R2" t="n">
-        <v>683</v>
+        <v>661</v>
       </c>
       <c r="S2" t="n">
-        <v>0.27374749498998</v>
+        <v>0.2720164609053498</v>
       </c>
       <c r="T2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U2" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03887775551102204</v>
+        <v>0.03909465020576132</v>
       </c>
       <c r="W2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="X2" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04849699398797595</v>
+        <v>0.0477366255144033</v>
       </c>
       <c r="Z2" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="AA2" t="n">
-        <v>856</v>
+        <v>837</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3430861723446894</v>
+        <v>0.3444444444444444</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.831712789827973</v>
+        <v>0.8332058148431523</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4494875549048316</v>
+        <v>0.4493192133131619</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3195876288659794</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3966942148760331</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3434579439252337</v>
+        <v>0.3393070489844683</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.663425579655946</v>
+        <v>1.666411629686305</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6391752577319587</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.050153531218014</v>
+        <v>1.038824763903463</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7701612903225806</v>
+        <v>0.02044989775051125</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.013806706114398</v>
+        <v>0.06072874493927125</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.721238938053097</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.452830188679245</v>
+        <v>1.439539347408829</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.70754716981132</v>
+        <v>4.664107485604607</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.160377358490566</v>
+        <v>6.103646833013435</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.61894736842105</v>
+        <v>75.74054054054054</v>
       </c>
       <c r="C3" t="n">
-        <v>75.51263157894738</v>
+        <v>75.63567567567569</v>
       </c>
       <c r="D3" t="n">
-        <v>115.9443522868255</v>
+        <v>115.6325486328488</v>
       </c>
       <c r="E3" t="n">
-        <v>114.167026778371</v>
+        <v>114.1674885296514</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5466933867735471</v>
+        <v>0.5452674897119341</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1567806136334055</v>
+        <v>0.1580512073777454</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3758339510748703</v>
+        <v>0.3765243902439024</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2400801603206413</v>
+        <v>0.2411522633744856</v>
       </c>
       <c r="J3" t="n">
-        <v>10.05263157894737</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="K3" t="n">
-        <v>13.52631578947368</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="L3" t="n">
-        <v>10.23684210526316</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="M3" t="n">
-        <v>12.60526315789474</v>
+        <v>12.7027027027027</v>
       </c>
       <c r="N3" t="n">
-        <v>29.26315789473684</v>
+        <v>29.43243243243243</v>
       </c>
       <c r="O3" t="n">
-        <v>35.18421052631579</v>
+        <v>35.32432432432432</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5358717434869739</v>
+        <v>0.5378600823045268</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.078947368421053</v>
+        <v>8.027027027027026</v>
       </c>
       <c r="R3" t="n">
-        <v>17.97368421052632</v>
+        <v>17.86486486486486</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2737474949899799</v>
+        <v>0.2720164609053498</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="U3" t="n">
-        <v>2.552631578947369</v>
+        <v>2.567567567567568</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03887775551102204</v>
+        <v>0.03909465020576131</v>
       </c>
       <c r="W3" t="n">
-        <v>1.263157894736842</v>
+        <v>1.243243243243243</v>
       </c>
       <c r="X3" t="n">
-        <v>3.184210526315789</v>
+        <v>3.135135135135135</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04849699398797595</v>
+        <v>0.04773662551440329</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.736842105263158</v>
+        <v>7.675675675675675</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.52631578947368</v>
+        <v>22.62162162162162</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3430861723446894</v>
+        <v>0.3444444444444444</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8317127898279731</v>
+        <v>0.8332058148431523</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4494875549048317</v>
+        <v>0.4493192133131619</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3195876288659794</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3966942148760331</v>
+        <v>0.396551724137931</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3434579439252336</v>
+        <v>0.3393070489844683</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.663425579655946</v>
+        <v>1.666411629686305</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6391752577319587</v>
+        <v>0.6315789473684211</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.050153531218014</v>
+        <v>1.038824763903463</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7701612903225806</v>
+        <v>0.02044989775051125</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.013806706114398</v>
+        <v>0.06072874493927126</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.721238938053097</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.452830188679245</v>
+        <v>1.439539347408829</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.707547169811321</v>
+        <v>4.664107485604607</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.160377358490567</v>
+        <v>6.103646833013436</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2865.440000000001</v>
+        <v>2794.64</v>
       </c>
       <c r="C4" t="n">
-        <v>2869.48</v>
+        <v>2798.52</v>
       </c>
       <c r="D4" t="n">
-        <v>114.167026778371</v>
+        <v>114.1674885296514</v>
       </c>
       <c r="E4" t="n">
-        <v>115.9443522868255</v>
+        <v>115.6325486328488</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5503508047874536</v>
+        <v>0.5506355932203389</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1516151908639621</v>
+        <v>0.1531647789916809</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3042813455657493</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2513413124226166</v>
+        <v>0.2525423728813559</v>
       </c>
       <c r="J4" t="n">
-        <v>443</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>448</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>345</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="N4" t="n">
-        <v>1104</v>
+        <v>1079</v>
       </c>
       <c r="O4" t="n">
-        <v>1303</v>
+        <v>1275</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5377631035905902</v>
+        <v>0.5402542372881356</v>
       </c>
       <c r="Q4" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="R4" t="n">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="S4" t="n">
-        <v>0.224927775484936</v>
+        <v>0.2254237288135593</v>
       </c>
       <c r="T4" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="U4" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04209657449442839</v>
+        <v>0.04067796610169491</v>
       </c>
       <c r="W4" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="X4" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05571605447791993</v>
+        <v>0.05466101694915254</v>
       </c>
       <c r="Z4" t="n">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="AA4" t="n">
-        <v>947</v>
+        <v>924</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3908378043747421</v>
+        <v>0.3915254237288135</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8472755180353031</v>
+        <v>0.8462745098039216</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4055045871559633</v>
+        <v>0.4078947368421053</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4509803921568628</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4370370370370371</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3400211193241816</v>
+        <v>0.3398268398268398</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.694551036070606</v>
+        <v>1.692549019607843</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.9019607843137255</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.05637707948244</v>
+        <v>1.056980056980057</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8358490566037736</v>
+        <v>0.03838771593090211</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.103448275862069</v>
+        <v>0.06532663316582915</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.674757281553398</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.469758064516129</v>
+        <v>1.458077709611452</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.88508064516129</v>
+        <v>4.826175869120655</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.354838709677419</v>
+        <v>6.284253578732106</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.40631578947369</v>
+        <v>75.53081081081082</v>
       </c>
       <c r="C5" t="n">
-        <v>75.51263157894738</v>
+        <v>75.63567567567569</v>
       </c>
       <c r="D5" t="n">
-        <v>114.167026778371</v>
+        <v>114.1674885296514</v>
       </c>
       <c r="E5" t="n">
-        <v>115.9443522868255</v>
+        <v>115.6325486328488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5503508047874536</v>
+        <v>0.5506355932203389</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1516151908639621</v>
+        <v>0.1531647789916809</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3042813455657493</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2513413124226166</v>
+        <v>0.2525423728813559</v>
       </c>
       <c r="J5" t="n">
-        <v>11.6578947368421</v>
+        <v>0.5405405405405406</v>
       </c>
       <c r="K5" t="n">
-        <v>11.78947368421053</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="L5" t="n">
-        <v>9.078947368421053</v>
+        <v>0.2972972972972973</v>
       </c>
       <c r="M5" t="n">
-        <v>11.52631578947368</v>
+        <v>11.7027027027027</v>
       </c>
       <c r="N5" t="n">
-        <v>29.05263157894737</v>
+        <v>29.16216216216216</v>
       </c>
       <c r="O5" t="n">
-        <v>34.28947368421053</v>
+        <v>34.45945945945946</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5377631035905902</v>
+        <v>0.5402542372881356</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.815789473684211</v>
+        <v>5.864864864864865</v>
       </c>
       <c r="R5" t="n">
-        <v>14.3421052631579</v>
+        <v>14.37837837837838</v>
       </c>
       <c r="S5" t="n">
-        <v>0.224927775484936</v>
+        <v>0.2254237288135593</v>
       </c>
       <c r="T5" t="n">
-        <v>1.210526315789474</v>
+        <v>1.162162162162162</v>
       </c>
       <c r="U5" t="n">
-        <v>2.684210526315789</v>
+        <v>2.594594594594595</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04209657449442839</v>
+        <v>0.04067796610169492</v>
       </c>
       <c r="W5" t="n">
-        <v>1.552631578947368</v>
+        <v>1.540540540540541</v>
       </c>
       <c r="X5" t="n">
-        <v>3.552631578947369</v>
+        <v>3.486486486486486</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05571605447791993</v>
+        <v>0.05466101694915254</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.473684210526315</v>
+        <v>8.486486486486486</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.92105263157895</v>
+        <v>24.97297297297297</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3908378043747421</v>
+        <v>0.3915254237288135</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8472755180353032</v>
+        <v>0.8462745098039215</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4055045871559633</v>
+        <v>0.4078947368421053</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4509803921568628</v>
+        <v>0.4479166666666666</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.437037037037037</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3400211193241816</v>
+        <v>0.3398268398268398</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.694551036070606</v>
+        <v>1.692549019607843</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.9019607843137255</v>
+        <v>0.8958333333333333</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.05637707948244</v>
+        <v>1.056980056980057</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8358490566037735</v>
+        <v>0.03838771593090212</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.103448275862069</v>
+        <v>0.06532663316582915</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.674757281553398</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.469758064516129</v>
+        <v>1.458077709611452</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.88508064516129</v>
+        <v>4.826175869120655</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.354838709677419</v>
+        <v>6.284253578732106</v>
       </c>
     </row>
     <row r="7">
@@ -1429,34 +1429,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="D8" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E8" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H8" t="n">
         <v>49</v>
       </c>
       <c r="I8" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J8" t="n">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="K8" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="L8" t="n">
         <v>31</v>
@@ -1471,49 +1471,49 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q8" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R8" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S8" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T8" t="n">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="U8" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>122</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>157</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="AB8" t="n">
         <v>34</v>
       </c>
-      <c r="Y8" t="n">
-        <v>124</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>35</v>
-      </c>
       <c r="AC8" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.376</v>
+        <v>0.37</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1534,57 +1534,57 @@
         <v>0.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AL8" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.321</v>
+        <v>0.319</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2176:33</t>
+          <t>1147:28</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>558.64</v>
+        <v>547.76</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.502</v>
+        <v>0.499</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.517</v>
+        <v>0.515</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.843</v>
+        <v>0.838</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.184</v>
+        <v>0.186</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.117</v>
+        <v>0.119</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.777</v>
+        <v>2.745</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.078</v>
+        <v>4.029</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.854</v>
+        <v>6.775</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.117</v>
+        <v>0.216</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.016</v>
+        <v>0.031</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.074</v>
+        <v>0.134</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.282</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="9">
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>65:16</t>
+          <t>35:33</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>2.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.095</v>
+        <v>0.174</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.105</v>
+        <v>0.193</v>
       </c>
       <c r="BA9" t="n">
         <v>0.003</v>
@@ -1816,16 +1816,16 @@
         <v>32</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>17</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>200:25</t>
+          <t>89:31</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>7</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.154</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.051</v>
+        <v>0.115</v>
       </c>
       <c r="BA10" t="n">
         <v>0.008</v>
@@ -1981,16 +1981,16 @@
         <v>10</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>2</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>181:09</t>
+          <t>79:39</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>6.333</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.096</v>
+        <v>0.218</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.013</v>
+        <v>0.029</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.044</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="n">
         <v>0.007</v>
@@ -2254,22 +2254,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="D13" t="n">
         <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="H13" t="n">
         <v>56</v>
@@ -2278,10 +2278,10 @@
         <v>69</v>
       </c>
       <c r="J13" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K13" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L13" t="n">
         <v>19</v>
@@ -2290,126 +2290,126 @@
         <v>20</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q13" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S13" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T13" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="U13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>98</v>
       </c>
       <c r="Z13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.784</v>
+        <v>0.79</v>
       </c>
       <c r="AB13" t="n">
         <v>42</v>
       </c>
       <c r="AC13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.452</v>
+        <v>0.457</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
       </c>
       <c r="AF13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.375</v>
+        <v>0.429</v>
       </c>
       <c r="AH13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.5</v>
+        <v>0.462</v>
       </c>
       <c r="AK13" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="AL13" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.351</v>
+        <v>0.329</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1278:56</t>
+          <t>593:40</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>428.36</v>
+        <v>414.36</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.528</v>
+        <v>0.515</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.964</v>
+        <v>0.946</v>
       </c>
       <c r="AS13" t="n">
         <v>0.14</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.166</v>
+        <v>0.172</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.933</v>
+        <v>1.931</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.633</v>
+        <v>5.621</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.567</v>
+        <v>7.552</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.152</v>
+        <v>0.317</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.017</v>
+        <v>0.036</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.042</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="14">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
@@ -2476,16 +2476,16 @@
         <v>73</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>22</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>700:10</t>
+          <t>299:00</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2565,13 +2565,13 @@
         <v>9.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.031</v>
+        <v>0.073</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.028</v>
+        <v>0.065</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.044</v>
+        <v>0.103</v>
       </c>
       <c r="BA14" t="n">
         <v>0.008</v>
@@ -2641,16 +2641,16 @@
         <v>25</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>11</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>315:56</t>
+          <t>146:16</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>5.833</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.099</v>
+        <v>0.215</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.018</v>
+        <v>0.039</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.036</v>
+        <v>0.078</v>
       </c>
       <c r="BA15" t="n">
         <v>0.013</v>
@@ -2749,91 +2749,91 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" t="n">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K16" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="M16" t="n">
         <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q16" t="n">
+        <v>54</v>
+      </c>
+      <c r="R16" t="n">
+        <v>84</v>
+      </c>
+      <c r="S16" t="n">
+        <v>60</v>
+      </c>
+      <c r="T16" t="n">
+        <v>263</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>55</v>
       </c>
-      <c r="R16" t="n">
-        <v>87</v>
-      </c>
-      <c r="S16" t="n">
-        <v>63</v>
-      </c>
-      <c r="T16" t="n">
-        <v>276</v>
-      </c>
-      <c r="U16" t="n">
-        <v>30</v>
-      </c>
-      <c r="V16" t="n">
+      <c r="Z16" t="n">
+        <v>72</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC16" t="n">
         <v>35</v>
       </c>
-      <c r="W16" t="n">
-        <v>21</v>
-      </c>
-      <c r="X16" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>56</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>38</v>
-      </c>
       <c r="AD16" t="n">
-        <v>0.474</v>
+        <v>0.486</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -2854,57 +2854,57 @@
         <v>0.533</v>
       </c>
       <c r="AK16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.378</v>
+        <v>0.366</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1756:29</t>
+          <t>858:12</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>252.56</v>
+        <v>244.68</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.58</v>
+        <v>0.578</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.899</v>
+        <v>0.891</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.226</v>
+        <v>0.229</v>
       </c>
       <c r="AT16" t="n">
         <v>0.19</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.246</v>
+        <v>1.25</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.053</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.298</v>
+        <v>4.25</v>
       </c>
       <c r="AX16" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="BA16" t="n">
         <v>0.065</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0.064</v>
       </c>
     </row>
     <row r="17">
@@ -2914,22 +2914,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H17" t="n">
         <v>8</v>
@@ -2962,25 +2962,25 @@
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S17" t="n">
         <v>19</v>
       </c>
       <c r="T17" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="U17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>16</v>
@@ -2995,10 +2995,10 @@
         <v>8</v>
       </c>
       <c r="AC17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.533</v>
+        <v>0.571</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3010,13 +3010,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.571</v>
+        <v>0.55</v>
       </c>
       <c r="AK17" t="n">
         <v>16</v>
@@ -3029,44 +3029,44 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>675:15</t>
+          <t>302:31</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>105.52</v>
+        <v>103.52</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.598</v>
+        <v>0.595</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.617</v>
+        <v>0.614</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.175</v>
+        <v>1.169</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.047</v>
+        <v>0.048</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AU17" t="n">
         <v>1.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.155</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.032</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.042</v>
+        <v>0.094</v>
       </c>
       <c r="BA17" t="n">
         <v>0.007</v>
@@ -3136,10 +3136,10 @@
         <v>41</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>165:54</t>
+          <t>86:00</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>9.333</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.097</v>
+        <v>0.186</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.041</v>
+        <v>0.079</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.062</v>
+        <v>0.12</v>
       </c>
       <c r="BA18" t="n">
         <v>0.001</v>
@@ -3240,20 +3240,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>#15 E. IZUNDU</t>
+          <t>#15 I. EBUKA</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>242</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -3262,79 +3262,79 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
         <v>18</v>
       </c>
-      <c r="Q19" t="n">
-        <v>18</v>
-      </c>
-      <c r="R19" t="n">
-        <v>71</v>
-      </c>
-      <c r="S19" t="n">
-        <v>57</v>
-      </c>
-      <c r="T19" t="n">
-        <v>326</v>
-      </c>
       <c r="U19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.873</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.627</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -3359,66 +3359,66 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>820:16</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>184.72</v>
+        <v>8</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.698</v>
+        <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.726</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.097</v>
+        <v>0.125</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.345</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.556</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.722</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.278</v>
+        <v>8</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.102</v>
+        <v>0.174</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.103</v>
+        <v>0.109</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.078</v>
+        <v>0.055</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>#15 I. EBUKA</t>
+          <t>#15 E. IZUNDU</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>236</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>137</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3427,49 +3427,49 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="T20" t="n">
-        <v>18</v>
+        <v>316</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
         <v>2</v>
@@ -3478,29 +3478,29 @@
         <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>113</v>
       </c>
       <c r="AA20" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
       <c r="AB20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>66</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2</v>
       </c>
-      <c r="AC20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
@@ -3524,47 +3524,47 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>40:53</t>
+          <t>422:15</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>8</v>
+        <v>180.52</v>
       </c>
       <c r="AP20" t="n">
-        <v>1</v>
+        <v>0.701</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1</v>
+        <v>0.726</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.75</v>
+        <v>1.307</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>0.321</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>0.556</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>7.611</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>8.167</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.089</v>
+        <v>0.194</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.056</v>
+        <v>0.197</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.028</v>
+        <v>0.143</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3904,16 +3904,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D23" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -3922,16 +3922,16 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I23" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L23" t="n">
         <v>21</v>
@@ -3952,43 +3952,43 @@
         <v>17</v>
       </c>
       <c r="R23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S23" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T23" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="W23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Z23" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.871</v>
+        <v>0.869</v>
       </c>
       <c r="AB23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4019,47 +4019,47 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>631:02</t>
+          <t>330:22</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>150.28</v>
+        <v>147.4</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.62</v>
+        <v>0.623</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.632</v>
+        <v>0.635</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.105</v>
+        <v>1.106</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.126</v>
+        <v>0.129</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.356</v>
+        <v>0.353</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.105</v>
+        <v>1.053</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.474</v>
+        <v>5.368</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.579</v>
+        <v>6.421</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.108</v>
+        <v>0.202</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.038</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.051</v>
+        <v>0.093</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="24">
@@ -4069,16 +4069,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E24" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -4087,25 +4087,25 @@
         <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>31</v>
+      </c>
+      <c r="L24" t="n">
+        <v>27</v>
+      </c>
+      <c r="M24" t="n">
         <v>4</v>
       </c>
-      <c r="K24" t="n">
-        <v>36</v>
-      </c>
-      <c r="L24" t="n">
-        <v>29</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6</v>
-      </c>
       <c r="N24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -4117,43 +4117,43 @@
         <v>16</v>
       </c>
       <c r="R24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T24" t="n">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="AB24" t="n">
         <v>5</v>
       </c>
-      <c r="Y24" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>8</v>
-      </c>
       <c r="AC24" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.533</v>
+        <v>0.455</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4184,47 +4184,47 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>478:54</t>
+          <t>187:34</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>78.72</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.64</v>
+        <v>0.663</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.654</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.042</v>
+        <v>1.052</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.203</v>
+        <v>0.231</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.158</v>
+        <v>0.163</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.562</v>
+        <v>3.062</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.812</v>
+        <v>3.188</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.075</v>
+        <v>0.168</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.189</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="25">
@@ -4234,43 +4234,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="D25" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E25" t="n">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F25" t="n">
         <v>61</v>
       </c>
       <c r="G25" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H25" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J25" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K25" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M25" t="n">
         <v>38</v>
       </c>
       <c r="N25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -4282,111 +4282,111 @@
         <v>72</v>
       </c>
       <c r="R25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S25" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="T25" t="n">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="U25" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="X25" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="n">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="Z25" t="n">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="AA25" t="n">
         <v>0.866</v>
       </c>
       <c r="AB25" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AC25" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.429</v>
+        <v>0.431</v>
       </c>
       <c r="AE25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AH25" t="n">
         <v>7</v>
       </c>
       <c r="AI25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.368</v>
+        <v>0.389</v>
       </c>
       <c r="AK25" t="n">
         <v>54</v>
       </c>
       <c r="AL25" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>1688:22</t>
+          <t>872:21</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>552.2</v>
+        <v>539</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.546</v>
+        <v>0.549</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.59</v>
+        <v>0.591</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.023</v>
+        <v>1.022</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.132</v>
+        <v>0.135</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.246</v>
+        <v>0.243</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.74</v>
+        <v>0.712</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.781</v>
+        <v>5.63</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.521</v>
+        <v>6.342</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.149</v>
+        <v>0.28</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.015</v>
+        <v>0.026</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="BA25" t="n">
         <v>0.054</v>
@@ -4399,22 +4399,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D26" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F26" t="n">
         <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H26" t="n">
         <v>53</v>
@@ -4432,7 +4432,7 @@
         <v>64</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N26" t="n">
         <v>28</v>
@@ -4441,40 +4441,40 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R26" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="S26" t="n">
         <v>62</v>
       </c>
       <c r="T26" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="U26" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z26" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.887</v>
+        <v>0.886</v>
       </c>
       <c r="AB26" t="n">
         <v>24</v>
@@ -4498,10 +4498,10 @@
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.238</v>
+        <v>0.263</v>
       </c>
       <c r="AK26" t="n">
         <v>23</v>
@@ -4514,47 +4514,47 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>1857:09</t>
+          <t>855:59</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>262.68</v>
+        <v>258.68</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.539</v>
+        <v>0.542</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.579</v>
+        <v>0.582</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.039</v>
+        <v>1.048</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.26</v>
+        <v>0.264</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.111</v>
+        <v>1.154</v>
       </c>
       <c r="AV26" t="n">
-        <v>7.556</v>
+        <v>7.731</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.667</v>
+        <v>8.885</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.064</v>
+        <v>0.137</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.039</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.044</v>
+        <v>0.095</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="27">
@@ -4729,16 +4729,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="D28" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E28" t="n">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
@@ -4747,22 +4747,22 @@
         <v>66</v>
       </c>
       <c r="H28" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I28" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J28" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K28" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="L28" t="n">
         <v>58</v>
       </c>
       <c r="M28" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N28" t="n">
         <v>27</v>
@@ -4771,49 +4771,49 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q28" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R28" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S28" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="T28" t="n">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="U28" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Z28" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.875</v>
+        <v>0.876</v>
       </c>
       <c r="AB28" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="AC28" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.493</v>
+        <v>0.485</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -4844,47 +4844,47 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>1709:09</t>
+          <t>888:38</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>420.28</v>
+        <v>409.52</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.607</v>
+        <v>0.606</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.671</v>
+        <v>0.673</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.144</v>
+        <v>1.145</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.529</v>
+        <v>0.537</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.097</v>
+        <v>1.082</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.452</v>
+        <v>4.393</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.548</v>
+        <v>5.475</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.112</v>
+        <v>0.209</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.039</v>
+        <v>0.074</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.108</v>
+        <v>0.203</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.066</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="29">
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" t="n">
         <v>65</v>
@@ -4903,13 +4903,13 @@
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H29" t="n">
         <v>16</v>
@@ -4918,13 +4918,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K29" t="n">
         <v>16</v>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
         <v>6</v>
@@ -4936,31 +4936,31 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R29" t="n">
         <v>33</v>
       </c>
       <c r="S29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T29" t="n">
         <v>45</v>
       </c>
       <c r="U29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>17</v>
@@ -4975,10 +4975,10 @@
         <v>6</v>
       </c>
       <c r="AC29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.333</v>
+        <v>0.353</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5002,54 +5002,54 @@
         <v>10</v>
       </c>
       <c r="AL29" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.196</v>
+        <v>0.2</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>638:16</t>
+          <t>258:17</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>118.92</v>
+        <v>114.92</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.302</v>
+        <v>0.31</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.365</v>
+        <v>0.374</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.547</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.252</v>
+        <v>0.244</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.198</v>
+        <v>0.203</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.867</v>
+        <v>1.929</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.7</v>
+        <v>2.821</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.567</v>
+        <v>4.75</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.202</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.029</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="30">
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -5086,10 +5086,10 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L30" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5220,163 +5220,163 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>3236</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>830</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1477</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>521</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>702</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>791</v>
       </c>
       <c r="T31" t="n">
-        <v>134</v>
+        <v>3899</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1089</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1307</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>661</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>0.449</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>0.397</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>837</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>0.339</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>7475:00</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>3296.4</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>0.982</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>4.664</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>6.104</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="BA31" t="n">
         <v>0</v>
@@ -5385,163 +5385,163 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" t="n">
-        <v>3327</v>
+        <v>3195</v>
       </c>
       <c r="D32" t="n">
-        <v>851</v>
+        <v>743</v>
       </c>
       <c r="E32" t="n">
-        <v>1518</v>
+        <v>1307</v>
       </c>
       <c r="F32" t="n">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="G32" t="n">
-        <v>977</v>
+        <v>1053</v>
       </c>
       <c r="H32" t="n">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="I32" t="n">
-        <v>808</v>
+        <v>781</v>
       </c>
       <c r="J32" t="n">
-        <v>770</v>
+        <v>713</v>
       </c>
       <c r="K32" t="n">
-        <v>938</v>
+        <v>818</v>
       </c>
       <c r="L32" t="n">
-        <v>507</v>
+        <v>398</v>
       </c>
       <c r="M32" t="n">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="N32" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>530</v>
+        <v>489</v>
       </c>
       <c r="Q32" t="n">
-        <v>479</v>
+        <v>433</v>
       </c>
       <c r="R32" t="n">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="S32" t="n">
-        <v>812</v>
+        <v>774</v>
       </c>
       <c r="T32" t="n">
-        <v>4013</v>
+        <v>3743</v>
       </c>
       <c r="U32" t="n">
-        <v>382</v>
+        <v>20</v>
       </c>
       <c r="V32" t="n">
-        <v>514</v>
+        <v>26</v>
       </c>
       <c r="W32" t="n">
-        <v>389</v>
+        <v>11</v>
       </c>
       <c r="X32" t="n">
-        <v>226</v>
+        <v>7</v>
       </c>
       <c r="Y32" t="n">
-        <v>1112</v>
+        <v>1079</v>
       </c>
       <c r="Z32" t="n">
-        <v>1337</v>
+        <v>1275</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.832</v>
+        <v>0.846</v>
       </c>
       <c r="AB32" t="n">
-        <v>307</v>
+        <v>217</v>
       </c>
       <c r="AC32" t="n">
-        <v>683</v>
+        <v>532</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.449</v>
+        <v>0.408</v>
       </c>
       <c r="AE32" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="AF32" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.32</v>
+        <v>0.448</v>
       </c>
       <c r="AH32" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="AI32" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.397</v>
+        <v>0.442</v>
       </c>
       <c r="AK32" t="n">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="n">
-        <v>856</v>
+        <v>924</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.343</v>
+        <v>0.34</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>7675:00</t>
+          <t>7475:00</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>3380.52</v>
+        <v>3192.64</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.547</v>
+        <v>0.551</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.584</v>
+        <v>0.591</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.984</v>
+        <v>1.001</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.157</v>
+        <v>0.153</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.24</v>
+        <v>0.253</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.453</v>
+        <v>1.458</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.708</v>
+        <v>4.826</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.16</v>
+        <v>6.284</v>
       </c>
       <c r="AX32" t="n">
         <v>0.2</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.075</v>
+        <v>0.061</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.14</v>
+        <v>0.125</v>
       </c>
       <c r="BA32" t="n">
         <v>0</v>
@@ -5550,460 +5550,460 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>38</v>
-      </c>
-      <c r="C33" t="n">
-        <v>3276</v>
-      </c>
-      <c r="D33" t="n">
-        <v>762</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1341</v>
-      </c>
-      <c r="F33" t="n">
-        <v>381</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1082</v>
-      </c>
-      <c r="H33" t="n">
-        <v>609</v>
-      </c>
-      <c r="I33" t="n">
-        <v>801</v>
-      </c>
-      <c r="J33" t="n">
-        <v>729</v>
-      </c>
-      <c r="K33" t="n">
-        <v>842</v>
-      </c>
-      <c r="L33" t="n">
-        <v>406</v>
-      </c>
-      <c r="M33" t="n">
-        <v>303</v>
-      </c>
-      <c r="N33" t="n">
-        <v>188</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>496</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>438</v>
-      </c>
-      <c r="R33" t="n">
-        <v>734</v>
-      </c>
-      <c r="S33" t="n">
-        <v>792</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3834</v>
-      </c>
-      <c r="U33" t="n">
-        <v>443</v>
-      </c>
-      <c r="V33" t="n">
-        <v>448</v>
-      </c>
-      <c r="W33" t="n">
-        <v>345</v>
-      </c>
-      <c r="X33" t="n">
-        <v>206</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1104</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1303</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>221</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>545</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>102</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>59</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>135</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>322</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>947</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>7675:00</t>
-        </is>
-      </c>
-      <c r="AO33" t="n">
-        <v>3271.44</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>4.885</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>6.355</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
-      <c r="BA34" t="inlineStr"/>
+          <t>#0 C. MILLER-MCINTYRE (Per Game)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>37</v>
+      </c>
+      <c r="C34" t="n">
+        <v>12.405</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.027</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5.838</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.676</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7.568</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.649</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.757</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T34" t="n">
+        <v>611</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>3.297</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.243</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.486</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.595</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>31:00</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>14.804</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4.029</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>6.775</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0.284</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#0 C. MILLER-MCINTYRE (Per Game)</t>
+          <t>#1 U. PLAVSIC (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C35" t="n">
-        <v>12.395</v>
+        <v>0.875</v>
       </c>
       <c r="D35" t="n">
-        <v>3.026</v>
+        <v>0.25</v>
       </c>
       <c r="E35" t="n">
-        <v>5.789</v>
+        <v>0.875</v>
       </c>
       <c r="F35" t="n">
-        <v>1.684</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>5.263</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.289</v>
+        <v>0.375</v>
       </c>
       <c r="I35" t="n">
-        <v>2.132</v>
+        <v>0.75</v>
       </c>
       <c r="J35" t="n">
-        <v>7.526</v>
+        <v>0.375</v>
       </c>
       <c r="K35" t="n">
-        <v>3.711</v>
+        <v>0.75</v>
       </c>
       <c r="L35" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.625</v>
       </c>
       <c r="M35" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="N35" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.711</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.395</v>
-      </c>
       <c r="S35" t="n">
-        <v>2.684</v>
+        <v>0.5</v>
       </c>
       <c r="T35" t="n">
-        <v>628</v>
+        <v>6</v>
       </c>
       <c r="U35" t="n">
-        <v>1.658</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.526</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.553</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.895</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.263</v>
+        <v>0.625</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.211</v>
+        <v>1.125</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.775</v>
+        <v>0.556</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.921</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.447</v>
+        <v>0.125</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.376</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.263</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.605</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>57:16</t>
+          <t>04:26</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>14.701</v>
+        <v>1.705</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.502</v>
+        <v>0.286</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.517</v>
+        <v>0.363</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.843</v>
+        <v>0.513</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.184</v>
+        <v>0.293</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.117</v>
+        <v>0.429</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.777</v>
+        <v>0.75</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.078</v>
+        <v>1.75</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.854</v>
+        <v>2.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.117</v>
+        <v>0.174</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.016</v>
+        <v>0.16</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.074</v>
+        <v>0.193</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.282</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#1 U. PLAVSIC (Per Game)</t>
+          <t>#2 S. MILJENOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C36" t="n">
-        <v>0.875</v>
+        <v>1.16</v>
       </c>
       <c r="D36" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="E36" t="n">
-        <v>0.875</v>
+        <v>0.36</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H36" t="n">
-        <v>0.375</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="J36" t="n">
-        <v>0.375</v>
+        <v>0.36</v>
       </c>
       <c r="K36" t="n">
-        <v>0.75</v>
+        <v>0.36</v>
       </c>
       <c r="L36" t="n">
-        <v>0.625</v>
+        <v>0.04</v>
       </c>
       <c r="M36" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="S36" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="T36" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -6012,19 +6012,19 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.625</v>
+        <v>0.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.125</v>
+        <v>0.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.556</v>
+        <v>0.85</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6048,54 +6048,54 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>03:34</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>1.705</v>
+        <v>1.219</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.286</v>
+        <v>0.395</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.363</v>
+        <v>0.548</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.513</v>
+        <v>0.951</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.293</v>
+        <v>0.131</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.429</v>
+        <v>0.737</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.75</v>
+        <v>4.75</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.095</v>
+        <v>0.154</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.105</v>
+        <v>0.115</v>
       </c>
       <c r="BA36" t="n">
         <v>0.012</v>
@@ -6104,92 +6104,92 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#2 S. MILJENOVIC (Per Game)</t>
+          <t>#4 D. GRAHAM (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="D37" t="n">
-        <v>0.12</v>
+        <v>0.083</v>
       </c>
       <c r="E37" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="F37" t="n">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="T37" t="n">
+        <v>10</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AA37" t="n">
         <v>0.4</v>
       </c>
-      <c r="H37" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T37" t="n">
-        <v>32</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.85</v>
-      </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.12</v>
+        <v>0.083</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -6207,154 +6207,154 @@
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.4</v>
+        <v>1.75</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.3</v>
+        <v>0.286</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>1.219</v>
+        <v>3.183</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.395</v>
+        <v>0.333</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.548</v>
+        <v>0.326</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.951</v>
+        <v>0.55</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.131</v>
+        <v>0.157</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.737</v>
+        <v>0.033</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.25</v>
+        <v>1.333</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AW37" t="n">
-        <v>7</v>
+        <v>6.333</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.218</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.006</v>
+        <v>0.029</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.051</v>
+        <v>0.1</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#4 D. GRAHAM (Per Game)</t>
+          <t>#5 A. NEDELJKOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.583</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -6372,127 +6372,127 @@
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>3.183</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.326</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.157</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.333</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.096</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#5 A. NEDELJKOVIC (Per Game)</t>
+          <t>#6 J. BUTLER (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>13.067</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>5.567</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1.867</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>3.733</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.633</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.933</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.867</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.367</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -6507,1083 +6507,1083 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>3.267</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4.133</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.067</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>0.457</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>0.433</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>4.867</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.329</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>13.812</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>0.515</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>0.946</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.931</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>5.621</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>7.552</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>0.317</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#6 J. BUTLER (Per Game)</t>
+          <t>#7 D. DAVIDOVAC (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C40" t="n">
-        <v>13.323</v>
+        <v>1.833</v>
       </c>
       <c r="D40" t="n">
-        <v>2.806</v>
+        <v>0.533</v>
       </c>
       <c r="E40" t="n">
-        <v>5.484</v>
+        <v>0.867</v>
       </c>
       <c r="F40" t="n">
-        <v>1.968</v>
+        <v>0.167</v>
       </c>
       <c r="G40" t="n">
-        <v>5.419</v>
+        <v>0.4</v>
       </c>
       <c r="H40" t="n">
-        <v>1.806</v>
+        <v>0.267</v>
       </c>
       <c r="I40" t="n">
-        <v>2.226</v>
+        <v>0.367</v>
       </c>
       <c r="J40" t="n">
-        <v>3.742</v>
+        <v>0.3</v>
       </c>
       <c r="K40" t="n">
-        <v>1.516</v>
+        <v>0.9</v>
       </c>
       <c r="L40" t="n">
-        <v>0.613</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>0.645</v>
+        <v>0.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0.516</v>
+        <v>0.067</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.935</v>
+        <v>0.167</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.871</v>
+        <v>0.167</v>
       </c>
       <c r="R40" t="n">
-        <v>2.355</v>
+        <v>1.2</v>
       </c>
       <c r="S40" t="n">
-        <v>2.355</v>
+        <v>0.5</v>
       </c>
       <c r="T40" t="n">
-        <v>368</v>
+        <v>73</v>
       </c>
       <c r="U40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.516</v>
+        <v>0.067</v>
       </c>
       <c r="W40" t="n">
-        <v>1.516</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.774</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>3.161</v>
+        <v>0.733</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.032</v>
+        <v>0.867</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.784</v>
+        <v>0.846</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.355</v>
+        <v>0.067</v>
       </c>
       <c r="AC40" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.452</v>
+        <v>0.333</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.258</v>
+        <v>0.067</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.226</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.452</v>
+        <v>0.067</v>
       </c>
       <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AM40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK40" t="n">
-        <v>1.742</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>4.968</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.351</v>
-      </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>41:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>13.818</v>
+        <v>1.595</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.528</v>
+        <v>0.618</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.642</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.964</v>
+        <v>1.15</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.14</v>
+        <v>0.105</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.166</v>
+        <v>0.211</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.933</v>
+        <v>1.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>5.633</v>
+        <v>7.6</v>
       </c>
       <c r="AW40" t="n">
-        <v>7.567</v>
+        <v>9.4</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.152</v>
+        <v>0.073</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.017</v>
+        <v>0.065</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.042</v>
+        <v>0.103</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.141</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#7 D. DAVIDOVAC (Per Game)</t>
+          <t>#11 T. CARTER (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C41" t="n">
-        <v>1.774</v>
+        <v>4.636</v>
       </c>
       <c r="D41" t="n">
-        <v>0.516</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.839</v>
+        <v>2.545</v>
       </c>
       <c r="F41" t="n">
-        <v>0.161</v>
+        <v>0.727</v>
       </c>
       <c r="G41" t="n">
-        <v>0.387</v>
+        <v>2.455</v>
       </c>
       <c r="H41" t="n">
-        <v>0.258</v>
+        <v>0.455</v>
       </c>
       <c r="I41" t="n">
-        <v>0.355</v>
+        <v>0.455</v>
       </c>
       <c r="J41" t="n">
-        <v>0.29</v>
+        <v>1.364</v>
       </c>
       <c r="K41" t="n">
-        <v>0.871</v>
+        <v>0.909</v>
       </c>
       <c r="L41" t="n">
-        <v>0.548</v>
+        <v>0.455</v>
       </c>
       <c r="M41" t="n">
-        <v>0.29</v>
+        <v>0.364</v>
       </c>
       <c r="N41" t="n">
-        <v>0.065</v>
+        <v>0.091</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.161</v>
+        <v>1.091</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.161</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.161</v>
+        <v>1.636</v>
       </c>
       <c r="S41" t="n">
-        <v>0.484</v>
+        <v>0.455</v>
       </c>
       <c r="T41" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="U41" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0.387</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.839</v>
+        <v>1.364</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.846</v>
+        <v>0.733</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.065</v>
+        <v>0.273</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.194</v>
+        <v>0.909</v>
       </c>
       <c r="AD41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="AM41" t="n">
         <v>0.333</v>
       </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>1.543</v>
+        <v>6.291</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.618</v>
+        <v>0.418</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.642</v>
+        <v>0.446</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.15</v>
+        <v>0.737</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.105</v>
+        <v>0.173</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.211</v>
+        <v>0.091</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AV41" t="n">
-        <v>7.6</v>
+        <v>4.583</v>
       </c>
       <c r="AW41" t="n">
-        <v>9.4</v>
+        <v>5.833</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.031</v>
+        <v>0.215</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.028</v>
+        <v>0.039</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.044</v>
+        <v>0.078</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#11 T. CARTER (Per Game)</t>
+          <t>#12 N. KALINIC (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C42" t="n">
-        <v>4.636</v>
+        <v>5.892</v>
       </c>
       <c r="D42" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.216</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.324</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.892</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.351</v>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="n">
-        <v>2.545</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2.455</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1.364</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.455</v>
-      </c>
       <c r="M42" t="n">
-        <v>0.364</v>
+        <v>0.541</v>
       </c>
       <c r="N42" t="n">
-        <v>0.091</v>
+        <v>0.486</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.091</v>
+        <v>1.514</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>1.459</v>
       </c>
       <c r="R42" t="n">
-        <v>1.636</v>
+        <v>2.27</v>
       </c>
       <c r="S42" t="n">
-        <v>0.455</v>
+        <v>1.622</v>
       </c>
       <c r="T42" t="n">
-        <v>25</v>
+        <v>263</v>
       </c>
       <c r="U42" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0.455</v>
+        <v>0.081</v>
       </c>
       <c r="W42" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1</v>
+        <v>1.486</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.364</v>
+        <v>1.946</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.733</v>
+        <v>0.764</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.273</v>
+        <v>0.459</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.909</v>
+        <v>0.946</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.3</v>
+        <v>0.486</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.182</v>
+        <v>0.054</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.727</v>
+        <v>0.189</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.091</v>
+        <v>0.216</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.545</v>
+        <v>0.405</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.167</v>
+        <v>0.533</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.636</v>
+        <v>0.703</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.909</v>
+        <v>1.919</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.333</v>
+        <v>0.366</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>28:43</t>
+          <t>23:11</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>6.291</v>
+        <v>6.613</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.418</v>
+        <v>0.554</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.446</v>
+        <v>0.578</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.737</v>
+        <v>0.891</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.173</v>
+        <v>0.229</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.091</v>
+        <v>0.19</v>
       </c>
       <c r="AU42" t="n">
         <v>1.25</v>
       </c>
       <c r="AV42" t="n">
-        <v>4.583</v>
+        <v>3</v>
       </c>
       <c r="AW42" t="n">
-        <v>5.833</v>
+        <v>4.25</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.099</v>
+        <v>0.129</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.018</v>
+        <v>0.049</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.036</v>
+        <v>0.116</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.046</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#12 N. KALINIC (Per Game)</t>
+          <t>#13 O. DOBRIC (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C43" t="n">
-        <v>5.974</v>
+        <v>5.042</v>
       </c>
       <c r="D43" t="n">
-        <v>1.132</v>
+        <v>0.667</v>
       </c>
       <c r="E43" t="n">
-        <v>2.237</v>
+        <v>1.417</v>
       </c>
       <c r="F43" t="n">
-        <v>0.947</v>
+        <v>1.125</v>
       </c>
       <c r="G43" t="n">
-        <v>2.342</v>
+        <v>2.542</v>
       </c>
       <c r="H43" t="n">
-        <v>0.868</v>
+        <v>0.333</v>
       </c>
       <c r="I43" t="n">
-        <v>1.289</v>
+        <v>0.333</v>
       </c>
       <c r="J43" t="n">
-        <v>1.868</v>
+        <v>0.333</v>
       </c>
       <c r="K43" t="n">
-        <v>2.368</v>
+        <v>1.042</v>
       </c>
       <c r="L43" t="n">
-        <v>1.079</v>
+        <v>0.792</v>
       </c>
       <c r="M43" t="n">
-        <v>0.526</v>
+        <v>0.417</v>
       </c>
       <c r="N43" t="n">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.5</v>
+        <v>0.208</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.447</v>
+        <v>0.167</v>
       </c>
       <c r="R43" t="n">
-        <v>2.289</v>
+        <v>1.208</v>
       </c>
       <c r="S43" t="n">
-        <v>1.658</v>
+        <v>0.792</v>
       </c>
       <c r="T43" t="n">
-        <v>276</v>
+        <v>119</v>
       </c>
       <c r="U43" t="n">
-        <v>0.789</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0.921</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.553</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.237</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.474</v>
+        <v>0.667</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.921</v>
+        <v>1.125</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.767</v>
+        <v>0.593</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.474</v>
+        <v>0.333</v>
       </c>
       <c r="AC43" t="n">
-        <v>1</v>
+        <v>0.583</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.474</v>
+        <v>0.571</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.184</v>
+        <v>0.042</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.211</v>
+        <v>0.458</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.395</v>
+        <v>0.833</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.533</v>
+        <v>0.55</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.737</v>
+        <v>0.667</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.947</v>
+        <v>1.708</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.378</v>
+        <v>0.39</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>46:13</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>6.646</v>
+        <v>4.313</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.595</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.58</v>
+        <v>0.614</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.899</v>
+        <v>1.169</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.226</v>
+        <v>0.048</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.19</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.246</v>
+        <v>1.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>3.053</v>
+        <v>19</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.298</v>
+        <v>20.6</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.065</v>
+        <v>0.155</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.027</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.059</v>
+        <v>0.094</v>
       </c>
       <c r="BA43" t="n">
-        <v>0.064</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#13 O. DOBRIC (Per Game)</t>
+          <t>#14 J. RIVERO (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>4.96</v>
+        <v>5.125</v>
       </c>
       <c r="D44" t="n">
-        <v>0.64</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>1.4</v>
+        <v>3.375</v>
       </c>
       <c r="F44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.32</v>
+        <v>1.125</v>
       </c>
       <c r="I44" t="n">
-        <v>0.32</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
-        <v>0.32</v>
+        <v>0.125</v>
       </c>
       <c r="K44" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S44" t="n">
         <v>1</v>
       </c>
-      <c r="L44" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N44" t="n">
+      <c r="T44" t="n">
+        <v>41</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AO44" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>9.333</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AZ44" t="n">
         <v>0.12</v>
       </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="T44" t="n">
-        <v>118</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>27:00</t>
-        </is>
-      </c>
-      <c r="AO44" t="n">
-        <v>4.221</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>0.042</v>
-      </c>
       <c r="BA44" t="n">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#14 J. RIVERO (Per Game)</t>
+          <t>#15 I. EBUKA (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>5.125</v>
+        <v>14</v>
       </c>
       <c r="D45" t="n">
+        <v>7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>7</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
         <v>2</v>
       </c>
-      <c r="E45" t="n">
-        <v>3.375</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.75</v>
-      </c>
       <c r="M45" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="U45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA45" t="n">
         <v>1</v>
       </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2.125</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0.895</v>
-      </c>
       <c r="AB45" t="n">
-        <v>0.875</v>
+        <v>2</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.875</v>
+        <v>2</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.467</v>
+        <v>1</v>
       </c>
       <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AO45" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS45" t="n">
         <v>0.125</v>
       </c>
-      <c r="AF45" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>20:44</t>
-        </is>
-      </c>
-      <c r="AO45" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>1.162</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0.08500000000000001</v>
-      </c>
       <c r="AT45" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="AV45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW45" t="n">
-        <v>9.333</v>
+        <v>8</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.097</v>
+        <v>0.174</v>
       </c>
       <c r="AY45" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="BA45" t="n">
         <v>0.041</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>0.004</v>
       </c>
     </row>
     <row r="46">
@@ -7593,16 +7593,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C46" t="n">
-        <v>7.333</v>
+        <v>7.375</v>
       </c>
       <c r="D46" t="n">
-        <v>2.939</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.212</v>
+        <v>4.281</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -7611,79 +7611,79 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.455</v>
+        <v>1.375</v>
       </c>
       <c r="I46" t="n">
-        <v>1.909</v>
+        <v>1.812</v>
       </c>
       <c r="J46" t="n">
-        <v>0.303</v>
+        <v>0.312</v>
       </c>
       <c r="K46" t="n">
-        <v>1.697</v>
+        <v>1.656</v>
       </c>
       <c r="L46" t="n">
-        <v>2.242</v>
+        <v>2.281</v>
       </c>
       <c r="M46" t="n">
-        <v>0.364</v>
+        <v>0.375</v>
       </c>
       <c r="N46" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="T46" t="n">
+        <v>316</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.531</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.062</v>
+      </c>
+      <c r="AD46" t="n">
         <v>0.636</v>
       </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="R46" t="n">
-        <v>2.152</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.727</v>
-      </c>
-      <c r="T46" t="n">
-        <v>326</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="V46" t="n">
-        <v>2.636</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0.424</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>3.121</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>3.576</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.273</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0.627</v>
-      </c>
       <c r="AE46" t="n">
         <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -7708,44 +7708,44 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>24:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>5.598</v>
+        <v>5.641</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.698</v>
+        <v>0.701</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.726</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.31</v>
+        <v>1.307</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.345</v>
+        <v>0.321</v>
       </c>
       <c r="AU46" t="n">
         <v>0.556</v>
       </c>
       <c r="AV46" t="n">
-        <v>7.722</v>
+        <v>7.611</v>
       </c>
       <c r="AW46" t="n">
-        <v>8.278</v>
+        <v>8.167</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.102</v>
+        <v>0.194</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.103</v>
+        <v>0.197</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.078</v>
+        <v>0.143</v>
       </c>
       <c r="BA46" t="n">
         <v>0.011</v>
@@ -7754,20 +7754,20 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#15 I. EBUKA (Per Game)</t>
+          <t>#17 L. STOJKOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C47" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -7782,16 +7782,16 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -7800,49 +7800,49 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7873,57 +7873,57 @@
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>40:53</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#17 L. STOJKOVIC (Per Game)</t>
+          <t>#18 N. PAVLOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -8084,71 +8084,71 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>#18 N. PAVLOVIC (Per Game)</t>
+          <t>#20 D. MOTIEJUNAS (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>5.621</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1.931</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>3.034</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.483</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1.241</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>2.069</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.931</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.724</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>0.931</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.552</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -8157,22 +8157,22 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.517</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.897</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>0.869</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.379</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.475</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8187,1380 +8187,1380 @@
         <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="AJ49" t="n">
         <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>0.448</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>5.083</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>0.623</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>0.635</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.106</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.053</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>5.368</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>6.421</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>#20 D. MOTIEJUNAS (Per Game)</t>
+          <t>#21 J. BOLOMBOY (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C50" t="n">
-        <v>5.533</v>
+        <v>5.615</v>
       </c>
       <c r="D50" t="n">
-        <v>1.9</v>
+        <v>2.154</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>3.385</v>
       </c>
       <c r="F50" t="n">
-        <v>0.167</v>
+        <v>0.231</v>
       </c>
       <c r="G50" t="n">
-        <v>0.467</v>
+        <v>0.385</v>
       </c>
       <c r="H50" t="n">
-        <v>1.233</v>
+        <v>0.615</v>
       </c>
       <c r="I50" t="n">
-        <v>2.067</v>
+        <v>0.769</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7</v>
+        <v>0.154</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9330000000000001</v>
+        <v>2.385</v>
       </c>
       <c r="L50" t="n">
-        <v>0.7</v>
+        <v>2.077</v>
       </c>
       <c r="M50" t="n">
-        <v>0.267</v>
+        <v>0.308</v>
       </c>
       <c r="N50" t="n">
-        <v>0.133</v>
+        <v>0.923</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.633</v>
+        <v>1.231</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5669999999999999</v>
+        <v>1.231</v>
       </c>
       <c r="R50" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.154</v>
       </c>
       <c r="S50" t="n">
-        <v>2.5</v>
+        <v>1.385</v>
       </c>
       <c r="T50" t="n">
-        <v>209</v>
+        <v>116</v>
       </c>
       <c r="U50" t="n">
-        <v>0.367</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.067</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.233</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.467</v>
+        <v>2.385</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.833</v>
+        <v>2.769</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.871</v>
+        <v>0.861</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.667</v>
+        <v>0.385</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.4</v>
+        <v>0.846</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.476</v>
+        <v>0.455</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.033</v>
+        <v>0.385</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>0.433</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>5.009</v>
+        <v>5.338</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.62</v>
+        <v>0.663</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.632</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.105</v>
+        <v>1.052</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.126</v>
+        <v>0.231</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.356</v>
+        <v>0.163</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.105</v>
+        <v>0.125</v>
       </c>
       <c r="AV50" t="n">
-        <v>5.474</v>
+        <v>3.062</v>
       </c>
       <c r="AW50" t="n">
-        <v>6.579</v>
+        <v>3.187</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.108</v>
+        <v>0.168</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.038</v>
+        <v>0.164</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.051</v>
+        <v>0.189</v>
       </c>
       <c r="BA50" t="n">
-        <v>0.024</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>#21 J. BOLOMBOY (Per Game)</t>
+          <t>#33 J. NWORA (Per Game)</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C51" t="n">
-        <v>5.857</v>
+        <v>17.219</v>
       </c>
       <c r="D51" t="n">
-        <v>2.286</v>
+        <v>4.188</v>
       </c>
       <c r="E51" t="n">
-        <v>3.714</v>
+        <v>7.656</v>
       </c>
       <c r="F51" t="n">
-        <v>0.214</v>
+        <v>1.906</v>
       </c>
       <c r="G51" t="n">
-        <v>0.357</v>
+        <v>5.188</v>
       </c>
       <c r="H51" t="n">
-        <v>0.643</v>
+        <v>3.125</v>
       </c>
       <c r="I51" t="n">
-        <v>0.929</v>
+        <v>3.906</v>
       </c>
       <c r="J51" t="n">
-        <v>0.286</v>
+        <v>1.625</v>
       </c>
       <c r="K51" t="n">
-        <v>2.571</v>
+        <v>3.875</v>
       </c>
       <c r="L51" t="n">
-        <v>2.071</v>
+        <v>0.625</v>
       </c>
       <c r="M51" t="n">
-        <v>0.429</v>
+        <v>1.188</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1.143</v>
+        <v>2.281</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.143</v>
+        <v>2.25</v>
       </c>
       <c r="R51" t="n">
-        <v>1.214</v>
+        <v>1.719</v>
       </c>
       <c r="S51" t="n">
-        <v>1.429</v>
+        <v>3.531</v>
       </c>
       <c r="T51" t="n">
-        <v>132</v>
+        <v>547</v>
       </c>
       <c r="U51" t="n">
-        <v>0.143</v>
+        <v>0.094</v>
       </c>
       <c r="V51" t="n">
-        <v>1.214</v>
+        <v>0.188</v>
       </c>
       <c r="W51" t="n">
-        <v>0.5</v>
+        <v>0.094</v>
       </c>
       <c r="X51" t="n">
-        <v>0.357</v>
+        <v>0.062</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.357</v>
+        <v>5.438</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.929</v>
+        <v>6.281</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.805</v>
+        <v>0.866</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.571</v>
+        <v>1.656</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.071</v>
+        <v>3.844</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.533</v>
+        <v>0.431</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.357</v>
+        <v>0.656</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.214</v>
+        <v>0.219</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.357</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.6</v>
+        <v>0.389</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.688</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>4.625</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>34:12</t>
+          <t>27:15</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>5.623</v>
+        <v>16.844</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.64</v>
+        <v>0.549</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.654</v>
+        <v>0.591</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.042</v>
+        <v>1.022</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.203</v>
+        <v>0.135</v>
       </c>
       <c r="AT51" t="n">
-        <v>0.158</v>
+        <v>0.243</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.25</v>
+        <v>0.712</v>
       </c>
       <c r="AV51" t="n">
-        <v>3.562</v>
+        <v>5.63</v>
       </c>
       <c r="AW51" t="n">
-        <v>3.812</v>
+        <v>6.342</v>
       </c>
       <c r="AX51" t="n">
-        <v>0.075</v>
+        <v>0.28</v>
       </c>
       <c r="AY51" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.026</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.162</v>
       </c>
       <c r="BA51" t="n">
-        <v>0.01</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>#33 J. NWORA (Per Game)</t>
+          <t>#37 S. OJELEYE (Per Game)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C52" t="n">
-        <v>17.121</v>
+        <v>7.324</v>
       </c>
       <c r="D52" t="n">
-        <v>4.212</v>
+        <v>1.811</v>
       </c>
       <c r="E52" t="n">
-        <v>7.667</v>
+        <v>3.378</v>
       </c>
       <c r="F52" t="n">
-        <v>1.848</v>
+        <v>0.757</v>
       </c>
       <c r="G52" t="n">
-        <v>5.121</v>
+        <v>2.054</v>
       </c>
       <c r="H52" t="n">
-        <v>3.152</v>
+        <v>1.432</v>
       </c>
       <c r="I52" t="n">
-        <v>3.939</v>
+        <v>1.946</v>
       </c>
       <c r="J52" t="n">
-        <v>1.636</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>3.788</v>
+        <v>1.919</v>
       </c>
       <c r="L52" t="n">
-        <v>0.667</v>
+        <v>1.73</v>
       </c>
       <c r="M52" t="n">
-        <v>1.152</v>
+        <v>0.486</v>
       </c>
       <c r="N52" t="n">
-        <v>0.576</v>
+        <v>0.757</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.212</v>
+        <v>0.703</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.182</v>
+        <v>0.676</v>
       </c>
       <c r="R52" t="n">
-        <v>1.697</v>
+        <v>1.622</v>
       </c>
       <c r="S52" t="n">
-        <v>3.545</v>
+        <v>1.676</v>
       </c>
       <c r="T52" t="n">
-        <v>563</v>
+        <v>333</v>
       </c>
       <c r="U52" t="n">
-        <v>2.515</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.758</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0.9389999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.485</v>
+        <v>2.514</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.333</v>
+        <v>2.838</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.866</v>
+        <v>0.886</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.636</v>
+        <v>0.649</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.818</v>
+        <v>1.757</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.429</v>
+        <v>0.369</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.242</v>
+        <v>0.081</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.667</v>
+        <v>0.216</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.364</v>
+        <v>0.375</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.212</v>
+        <v>0.135</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.576</v>
+        <v>0.514</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.368</v>
+        <v>0.263</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.636</v>
+        <v>0.622</v>
       </c>
       <c r="AL52" t="n">
-        <v>4.545</v>
+        <v>1.541</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.36</v>
+        <v>0.404</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>51:09</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>16.733</v>
+        <v>6.991</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.546</v>
+        <v>0.542</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.59</v>
+        <v>0.582</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.023</v>
+        <v>1.048</v>
       </c>
       <c r="AS52" t="n">
-        <v>0.132</v>
+        <v>0.101</v>
       </c>
       <c r="AT52" t="n">
-        <v>0.246</v>
+        <v>0.264</v>
       </c>
       <c r="AU52" t="n">
-        <v>0.74</v>
+        <v>1.154</v>
       </c>
       <c r="AV52" t="n">
-        <v>5.781</v>
+        <v>7.731</v>
       </c>
       <c r="AW52" t="n">
-        <v>6.521</v>
+        <v>8.885</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.149</v>
+        <v>0.137</v>
       </c>
       <c r="AY52" t="n">
-        <v>0.015</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.095</v>
       </c>
       <c r="BA52" t="n">
-        <v>0.065</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>#37 S. OJELEYE (Per Game)</t>
+          <t>#44 O. RADOSIC (Per Game)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C53" t="n">
-        <v>7.184</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>1.789</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>3.316</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.737</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>2.053</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.395</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1.895</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0.789</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1.868</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>1.684</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0.737</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.711</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.6840000000000001</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.632</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.632</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.658</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0.342</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.474</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.789</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.887</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.711</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.369</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.553</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.238</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>0.605</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.404</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>48:52</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="AO53" t="n">
-        <v>6.913</v>
+        <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.539</v>
+        <v>0</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.039</v>
+        <v>0</v>
       </c>
       <c r="AS53" t="n">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="AT53" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.111</v>
+        <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>7.556</v>
+        <v>0</v>
       </c>
       <c r="AW53" t="n">
-        <v>8.667</v>
+        <v>0</v>
       </c>
       <c r="AX53" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="AY53" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="BA53" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>#44 O. RADOSIC (Per Game)</t>
+          <t>#95 C. MONEKE (Per Game)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>13.794</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>3.765</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>5.941</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>0.676</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1.941</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>4.235</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>5.382</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1.941</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>4.647</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.706</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>0.971</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>0.794</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.794</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1.647</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.206</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>4.235</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>663</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>6.853</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>7.824</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>0.876</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>0.971</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>0.647</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1.882</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>26:08</t>
         </is>
       </c>
       <c r="AO54" t="n">
-        <v>0</v>
+        <v>12.045</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>0.606</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>0.673</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.145</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>0.537</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>1.082</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>4.393</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>5.475</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>0.209</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>0.203</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>#95 C. MONEKE (Per Game)</t>
+          <t>#99 Y. DOS SANTOS (Per Game)</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C55" t="n">
-        <v>13.743</v>
+        <v>2.321</v>
       </c>
       <c r="D55" t="n">
-        <v>3.8</v>
+        <v>0.286</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>0.964</v>
       </c>
       <c r="F55" t="n">
-        <v>0.657</v>
+        <v>0.393</v>
       </c>
       <c r="G55" t="n">
-        <v>1.886</v>
+        <v>1.857</v>
       </c>
       <c r="H55" t="n">
-        <v>4.171</v>
+        <v>0.571</v>
       </c>
       <c r="I55" t="n">
-        <v>5.343</v>
+        <v>0.643</v>
       </c>
       <c r="J55" t="n">
-        <v>1.943</v>
+        <v>1.929</v>
       </c>
       <c r="K55" t="n">
-        <v>4.629</v>
+        <v>0.571</v>
       </c>
       <c r="L55" t="n">
-        <v>1.657</v>
+        <v>0.107</v>
       </c>
       <c r="M55" t="n">
-        <v>0.971</v>
+        <v>0.214</v>
       </c>
       <c r="N55" t="n">
-        <v>0.771</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.771</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.657</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>2.2</v>
+        <v>1.179</v>
       </c>
       <c r="S55" t="n">
-        <v>4.229</v>
+        <v>0.786</v>
       </c>
       <c r="T55" t="n">
-        <v>678</v>
+        <v>45</v>
       </c>
       <c r="U55" t="n">
-        <v>1.857</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.514</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.657</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.857</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>6.771</v>
+        <v>0.607</v>
       </c>
       <c r="Z55" t="n">
-        <v>7.743</v>
+        <v>0.821</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.875</v>
+        <v>0.739</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.029</v>
+        <v>0.214</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.086</v>
+        <v>0.607</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.493</v>
+        <v>0.353</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.171</v>
+        <v>0.036</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.343</v>
+        <v>0.107</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.029</v>
+        <v>0.036</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.057</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AJ55" t="n">
         <v>0.5</v>
       </c>
       <c r="AK55" t="n">
-        <v>0.629</v>
+        <v>0.357</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.829</v>
+        <v>1.786</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.344</v>
+        <v>0.2</v>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>48:49</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>12.008</v>
+        <v>4.104</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.607</v>
+        <v>0.31</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.671</v>
+        <v>0.374</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.144</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.148</v>
+        <v>0.244</v>
       </c>
       <c r="AT55" t="n">
-        <v>0.529</v>
+        <v>0.203</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.097</v>
+        <v>1.929</v>
       </c>
       <c r="AV55" t="n">
-        <v>4.452</v>
+        <v>2.821</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.548</v>
+        <v>4.75</v>
       </c>
       <c r="AX55" t="n">
-        <v>0.112</v>
+        <v>0.202</v>
       </c>
       <c r="AY55" t="n">
-        <v>0.039</v>
+        <v>0.013</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0.108</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="BA55" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>#99 Y. DOS SANTOS (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C56" t="n">
-        <v>2.241</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.276</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.966</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.379</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>1.828</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.552</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0.621</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1.931</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.552</v>
+        <v>1.865</v>
       </c>
       <c r="L56" t="n">
-        <v>0.138</v>
+        <v>2.27</v>
       </c>
       <c r="M56" t="n">
-        <v>0.207</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.034</v>
+        <v>0.649</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.034</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.138</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.793</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>0.379</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>0.448</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>0.241</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.793</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.739</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.207</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.621</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>0.345</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.759</v>
+        <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.196</v>
+        <v>0</v>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO56" t="n">
-        <v>4.101</v>
+        <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.365</v>
+        <v>0</v>
       </c>
       <c r="AR56" t="n">
-        <v>0.547</v>
+        <v>0</v>
       </c>
       <c r="AS56" t="n">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="AT56" t="n">
-        <v>0.198</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.867</v>
+        <v>0</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>4.567</v>
+        <v>0</v>
       </c>
       <c r="AX56" t="n">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY56" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="BA56" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>87.459</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>22.432</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>39.919</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>8.919</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>25.757</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>15.838</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>21.216</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>20.27</v>
       </c>
       <c r="K57" t="n">
-        <v>1.895</v>
+        <v>24.595</v>
       </c>
       <c r="L57" t="n">
-        <v>2.289</v>
+        <v>13.351</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>6.162</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.919</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0.658</v>
+        <v>14.081</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>12.703</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>18.973</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>21.378</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3899</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>29.432</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>35.324</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>8.026999999999999</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>17.865</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>0.449</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.568</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.243</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>3.135</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>0.397</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>7.676</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>22.622</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>0.339</v>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>202:01</t>
         </is>
       </c>
       <c r="AO57" t="n">
-        <v>0</v>
+        <v>89.092</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>0.583</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>0.982</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>4.664</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>6.104</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="BA57" t="n">
         <v>0</v>
@@ -9569,495 +9569,165 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>86.351</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>20.081</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>35.324</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>10.027</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>28.459</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>16.108</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>21.108</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>19.27</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>22.108</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>10.757</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.919</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>13.216</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>11.703</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>19.27</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>20.919</v>
       </c>
       <c r="T58" t="n">
-        <v>134</v>
+        <v>3743</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>0.541</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>0.703</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>0.297</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>29.162</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>34.459</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>5.865</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>14.378</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>0.408</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.162</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.595</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>0.448</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.541</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>3.486</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>0.442</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>8.486000000000001</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>24.973</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>202:01</t>
         </is>
       </c>
       <c r="AO58" t="n">
-        <v>0.658</v>
+        <v>86.288</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>0.551</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>1.001</v>
       </c>
       <c r="AS58" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>1.458</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>4.826</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>6.284</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>38</v>
-      </c>
-      <c r="C59" t="n">
-        <v>87.553</v>
-      </c>
-      <c r="D59" t="n">
-        <v>22.395</v>
-      </c>
-      <c r="E59" t="n">
-        <v>39.947</v>
-      </c>
-      <c r="F59" t="n">
-        <v>9</v>
-      </c>
-      <c r="G59" t="n">
-        <v>25.711</v>
-      </c>
-      <c r="H59" t="n">
-        <v>15.763</v>
-      </c>
-      <c r="I59" t="n">
-        <v>21.263</v>
-      </c>
-      <c r="J59" t="n">
-        <v>20.263</v>
-      </c>
-      <c r="K59" t="n">
-        <v>24.684</v>
-      </c>
-      <c r="L59" t="n">
-        <v>13.342</v>
-      </c>
-      <c r="M59" t="n">
-        <v>6.105</v>
-      </c>
-      <c r="N59" t="n">
-        <v>4.947</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>13.947</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>12.605</v>
-      </c>
-      <c r="R59" t="n">
-        <v>18.947</v>
-      </c>
-      <c r="S59" t="n">
-        <v>21.368</v>
-      </c>
-      <c r="T59" t="n">
-        <v>4013</v>
-      </c>
-      <c r="U59" t="n">
-        <v>10.053</v>
-      </c>
-      <c r="V59" t="n">
-        <v>13.526</v>
-      </c>
-      <c r="W59" t="n">
-        <v>10.237</v>
-      </c>
-      <c r="X59" t="n">
-        <v>5.947</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>29.263</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>35.184</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0.832</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>8.079000000000001</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>17.974</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>2.553</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.263</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>3.184</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>7.737</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>22.526</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>201:58</t>
-        </is>
-      </c>
-      <c r="AO59" t="n">
-        <v>88.961</v>
-      </c>
-      <c r="AP59" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>1.453</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>4.708</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>38</v>
-      </c>
-      <c r="C60" t="n">
-        <v>86.211</v>
-      </c>
-      <c r="D60" t="n">
-        <v>20.053</v>
-      </c>
-      <c r="E60" t="n">
-        <v>35.289</v>
-      </c>
-      <c r="F60" t="n">
-        <v>10.026</v>
-      </c>
-      <c r="G60" t="n">
-        <v>28.474</v>
-      </c>
-      <c r="H60" t="n">
-        <v>16.026</v>
-      </c>
-      <c r="I60" t="n">
-        <v>21.079</v>
-      </c>
-      <c r="J60" t="n">
-        <v>19.184</v>
-      </c>
-      <c r="K60" t="n">
-        <v>22.158</v>
-      </c>
-      <c r="L60" t="n">
-        <v>10.684</v>
-      </c>
-      <c r="M60" t="n">
-        <v>7.974</v>
-      </c>
-      <c r="N60" t="n">
-        <v>4.947</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>13.053</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>11.526</v>
-      </c>
-      <c r="R60" t="n">
-        <v>19.316</v>
-      </c>
-      <c r="S60" t="n">
-        <v>20.842</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3834</v>
-      </c>
-      <c r="U60" t="n">
-        <v>11.658</v>
-      </c>
-      <c r="V60" t="n">
-        <v>11.789</v>
-      </c>
-      <c r="W60" t="n">
-        <v>9.079000000000001</v>
-      </c>
-      <c r="X60" t="n">
-        <v>5.421</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>29.053</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>34.289</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>5.816</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>14.342</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>1.211</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>2.684</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>1.553</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>3.553</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>8.474</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>24.921</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>201:58</t>
-        </is>
-      </c>
-      <c r="AO60" t="n">
-        <v>86.09099999999999</v>
-      </c>
-      <c r="AP60" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AQ60" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>4.885</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>6.355</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="BA60" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
@@ -671,13 +671,13 @@
         <v>0.2411522633744856</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>384</v>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="M2" t="n">
         <v>470</v>
@@ -752,13 +752,13 @@
         <v>1.038824763903463</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.02044989775051125</v>
+        <v>0.7852760736196319</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.06072874493927125</v>
+        <v>1.036437246963563</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>1.704035874439462</v>
       </c>
       <c r="AN2" t="n">
         <v>1.439539347408829</v>
@@ -801,13 +801,13 @@
         <v>0.2411522633744856</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2702702702702703</v>
+        <v>10.37837837837838</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8108108108108109</v>
+        <v>13.83783783783784</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2702702702702703</v>
+        <v>10.27027027027027</v>
       </c>
       <c r="M3" t="n">
         <v>12.7027027027027</v>
@@ -882,13 +882,13 @@
         <v>1.038824763903463</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02044989775051125</v>
+        <v>0.7852760736196319</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.06072874493927126</v>
+        <v>1.036437246963563</v>
       </c>
       <c r="AM3" t="n">
-        <v>2</v>
+        <v>1.704035874439462</v>
       </c>
       <c r="AN3" t="n">
         <v>1.439539347408829</v>
@@ -931,13 +931,13 @@
         <v>0.2525423728813559</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>458</v>
       </c>
       <c r="K4" t="n">
-        <v>26</v>
+        <v>439</v>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>340</v>
       </c>
       <c r="M4" t="n">
         <v>433</v>
@@ -1012,13 +1012,13 @@
         <v>1.056980056980057</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03838771593090211</v>
+        <v>0.8790786948176583</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.06532663316582915</v>
+        <v>1.103015075376884</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.571428571428571</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AN4" t="n">
         <v>1.458077709611452</v>
@@ -1061,13 +1061,13 @@
         <v>0.2525423728813559</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5405405405405406</v>
+        <v>12.37837837837838</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7027027027027027</v>
+        <v>11.86486486486486</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2972972972972973</v>
+        <v>9.189189189189189</v>
       </c>
       <c r="M5" t="n">
         <v>11.7027027027027</v>
@@ -1142,13 +1142,13 @@
         <v>1.056980056980057</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.03838771593090212</v>
+        <v>0.8790786948176584</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.06532663316582915</v>
+        <v>1.103015075376885</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.571428571428571</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AN5" t="n">
         <v>1.458077709611452</v>
@@ -1486,16 +1486,16 @@
         <v>611</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="Y8" t="n">
         <v>122</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1816,16 +1816,16 @@
         <v>32</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="n">
         <v>17</v>
@@ -1981,16 +1981,16 @@
         <v>10</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
         <v>2</v>
@@ -2311,16 +2311,16 @@
         <v>346</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="n">
         <v>98</v>
@@ -2476,16 +2476,16 @@
         <v>73</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>22</v>
@@ -2641,16 +2641,16 @@
         <v>25</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
         <v>11</v>
@@ -2806,16 +2806,16 @@
         <v>263</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="n">
         <v>55</v>
@@ -2971,16 +2971,16 @@
         <v>119</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y17" t="n">
         <v>16</v>
@@ -3136,10 +3136,10 @@
         <v>41</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3301,16 +3301,16 @@
         <v>18</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
@@ -3466,16 +3466,16 @@
         <v>316</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="n">
         <v>98</v>
@@ -3961,16 +3961,16 @@
         <v>206</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="V23" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y23" t="n">
         <v>73</v>
@@ -4126,16 +4126,16 @@
         <v>116</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
         <v>31</v>
@@ -4291,16 +4291,16 @@
         <v>547</v>
       </c>
       <c r="U25" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="Y25" t="n">
         <v>174</v>
@@ -4456,16 +4456,16 @@
         <v>333</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y26" t="n">
         <v>93</v>
@@ -4786,16 +4786,16 @@
         <v>663</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="W28" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="Y28" t="n">
         <v>233</v>
@@ -4951,16 +4951,16 @@
         <v>45</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y29" t="n">
         <v>17</v>
@@ -5281,16 +5281,16 @@
         <v>3899</v>
       </c>
       <c r="U31" t="n">
-        <v>10</v>
+        <v>384</v>
       </c>
       <c r="V31" t="n">
-        <v>30</v>
+        <v>512</v>
       </c>
       <c r="W31" t="n">
-        <v>10</v>
+        <v>380</v>
       </c>
       <c r="X31" t="n">
-        <v>5</v>
+        <v>223</v>
       </c>
       <c r="Y31" t="n">
         <v>1089</v>
@@ -5446,16 +5446,16 @@
         <v>3743</v>
       </c>
       <c r="U32" t="n">
-        <v>20</v>
+        <v>458</v>
       </c>
       <c r="V32" t="n">
-        <v>26</v>
+        <v>439</v>
       </c>
       <c r="W32" t="n">
-        <v>11</v>
+        <v>340</v>
       </c>
       <c r="X32" t="n">
-        <v>7</v>
+        <v>204</v>
       </c>
       <c r="Y32" t="n">
         <v>1079</v>
@@ -5670,16 +5670,16 @@
         <v>611</v>
       </c>
       <c r="U34" t="n">
-        <v>0.081</v>
+        <v>1.703</v>
       </c>
       <c r="V34" t="n">
-        <v>0.135</v>
+        <v>1.649</v>
       </c>
       <c r="W34" t="n">
-        <v>0.081</v>
+        <v>1.568</v>
       </c>
       <c r="X34" t="n">
-        <v>0.027</v>
+        <v>0.919</v>
       </c>
       <c r="Y34" t="n">
         <v>3.297</v>
@@ -5838,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -6000,16 +6000,16 @@
         <v>32</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Y36" t="n">
         <v>0.68</v>
@@ -6165,16 +6165,16 @@
         <v>10</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y37" t="n">
         <v>0.167</v>
@@ -6495,16 +6495,16 @@
         <v>346</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.133</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.467</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.467</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.767</v>
       </c>
       <c r="Y39" t="n">
         <v>3.267</v>
@@ -6660,16 +6660,16 @@
         <v>73</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V40" t="n">
-        <v>0.067</v>
+        <v>0.367</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="Y40" t="n">
         <v>0.733</v>
@@ -6825,16 +6825,16 @@
         <v>25</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="Y41" t="n">
         <v>1</v>
@@ -6990,16 +6990,16 @@
         <v>263</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="V42" t="n">
-        <v>0.081</v>
+        <v>0.946</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="Y42" t="n">
         <v>1.486</v>
@@ -7155,16 +7155,16 @@
         <v>119</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y43" t="n">
         <v>0.667</v>
@@ -7320,10 +7320,10 @@
         <v>41</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -7485,16 +7485,16 @@
         <v>18</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
         <v>5</v>
@@ -7650,16 +7650,16 @@
         <v>316</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0.25</v>
+        <v>2.688</v>
       </c>
       <c r="W46" t="n">
-        <v>0.062</v>
+        <v>0.438</v>
       </c>
       <c r="X46" t="n">
-        <v>0.031</v>
+        <v>0.312</v>
       </c>
       <c r="Y46" t="n">
         <v>3.062</v>
@@ -8145,16 +8145,16 @@
         <v>206</v>
       </c>
       <c r="U49" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.414</v>
       </c>
       <c r="V49" t="n">
-        <v>0.138</v>
+        <v>1.138</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>0.414</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="Y49" t="n">
         <v>2.517</v>
@@ -8310,16 +8310,16 @@
         <v>116</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="Y50" t="n">
         <v>2.385</v>
@@ -8475,16 +8475,16 @@
         <v>547</v>
       </c>
       <c r="U51" t="n">
-        <v>0.094</v>
+        <v>2.75</v>
       </c>
       <c r="V51" t="n">
-        <v>0.188</v>
+        <v>1.75</v>
       </c>
       <c r="W51" t="n">
-        <v>0.094</v>
+        <v>1.844</v>
       </c>
       <c r="X51" t="n">
-        <v>0.062</v>
+        <v>1.031</v>
       </c>
       <c r="Y51" t="n">
         <v>5.438</v>
@@ -8640,16 +8640,16 @@
         <v>333</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.568</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="Y52" t="n">
         <v>2.514</v>
@@ -8970,16 +8970,16 @@
         <v>663</v>
       </c>
       <c r="U54" t="n">
-        <v>0.059</v>
+        <v>1.824</v>
       </c>
       <c r="V54" t="n">
-        <v>0.059</v>
+        <v>1.618</v>
       </c>
       <c r="W54" t="n">
-        <v>0.059</v>
+        <v>2.647</v>
       </c>
       <c r="X54" t="n">
-        <v>0.029</v>
+        <v>1.882</v>
       </c>
       <c r="Y54" t="n">
         <v>6.853</v>
@@ -9135,16 +9135,16 @@
         <v>45</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>0.393</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>0.464</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>0.321</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Y55" t="n">
         <v>0.607</v>
@@ -9465,16 +9465,16 @@
         <v>3899</v>
       </c>
       <c r="U57" t="n">
-        <v>0.27</v>
+        <v>10.378</v>
       </c>
       <c r="V57" t="n">
-        <v>0.8110000000000001</v>
+        <v>13.838</v>
       </c>
       <c r="W57" t="n">
-        <v>0.27</v>
+        <v>10.27</v>
       </c>
       <c r="X57" t="n">
-        <v>0.135</v>
+        <v>6.027</v>
       </c>
       <c r="Y57" t="n">
         <v>29.432</v>
@@ -9630,16 +9630,16 @@
         <v>3743</v>
       </c>
       <c r="U58" t="n">
-        <v>0.541</v>
+        <v>12.378</v>
       </c>
       <c r="V58" t="n">
-        <v>0.703</v>
+        <v>11.865</v>
       </c>
       <c r="W58" t="n">
-        <v>0.297</v>
+        <v>9.189</v>
       </c>
       <c r="X58" t="n">
-        <v>0.189</v>
+        <v>5.514</v>
       </c>
       <c r="Y58" t="n">
         <v>29.162</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2802.4</v>
+        <v>2873.52</v>
       </c>
       <c r="C2" t="n">
-        <v>2798.52</v>
+        <v>2869.48</v>
       </c>
       <c r="D2" t="n">
-        <v>115.6325486328488</v>
+        <v>115.9443522868255</v>
       </c>
       <c r="E2" t="n">
-        <v>114.1674885296514</v>
+        <v>114.167026778371</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5452674897119342</v>
+        <v>0.5466933867735471</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1580512073777454</v>
+        <v>0.1567806136334055</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3765243902439024</v>
+        <v>0.3758339510748703</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2411522633744856</v>
+        <v>0.2400801603206413</v>
       </c>
       <c r="J2" t="n">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="L2" t="n">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="M2" t="n">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="N2" t="n">
-        <v>1089</v>
+        <v>1112</v>
       </c>
       <c r="O2" t="n">
-        <v>1307</v>
+        <v>1337</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5378600823045268</v>
+        <v>0.535871743486974</v>
       </c>
       <c r="Q2" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="R2" t="n">
-        <v>661</v>
+        <v>683</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2720164609053498</v>
+        <v>0.27374749498998</v>
       </c>
       <c r="T2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U2" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03909465020576132</v>
+        <v>0.03887775551102204</v>
       </c>
       <c r="W2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="X2" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0477366255144033</v>
+        <v>0.04849699398797595</v>
       </c>
       <c r="Z2" t="n">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="AA2" t="n">
-        <v>837</v>
+        <v>856</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3444444444444444</v>
+        <v>0.3430861723446894</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8332058148431523</v>
+        <v>0.831712789827973</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4493192133131619</v>
+        <v>0.4494875549048316</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3195876288659794</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.396551724137931</v>
+        <v>0.3966942148760331</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3393070489844683</v>
+        <v>0.3434579439252337</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.666411629686305</v>
+        <v>1.663425579655946</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6391752577319587</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.038824763903463</v>
+        <v>1.050153531218014</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7852760736196319</v>
+        <v>0.7943548387096774</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.036437246963563</v>
+        <v>1.03353057199211</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.704035874439462</v>
+        <v>1.714912280701754</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.439539347408829</v>
+        <v>1.452830188679245</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.664107485604607</v>
+        <v>4.70754716981132</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.103646833013435</v>
+        <v>6.160377358490566</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.74054054054054</v>
+        <v>75.61894736842105</v>
       </c>
       <c r="C3" t="n">
-        <v>75.63567567567569</v>
+        <v>75.51263157894738</v>
       </c>
       <c r="D3" t="n">
-        <v>115.6325486328488</v>
+        <v>115.9443522868255</v>
       </c>
       <c r="E3" t="n">
-        <v>114.1674885296514</v>
+        <v>114.167026778371</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5452674897119341</v>
+        <v>0.5466933867735471</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1580512073777454</v>
+        <v>0.1567806136334055</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3765243902439024</v>
+        <v>0.3758339510748703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2411522633744856</v>
+        <v>0.2400801603206413</v>
       </c>
       <c r="J3" t="n">
-        <v>10.37837837837838</v>
+        <v>10.36842105263158</v>
       </c>
       <c r="K3" t="n">
-        <v>13.83783783783784</v>
+        <v>13.78947368421053</v>
       </c>
       <c r="L3" t="n">
-        <v>10.27027027027027</v>
+        <v>10.28947368421053</v>
       </c>
       <c r="M3" t="n">
-        <v>12.7027027027027</v>
+        <v>12.57894736842105</v>
       </c>
       <c r="N3" t="n">
-        <v>29.43243243243243</v>
+        <v>29.26315789473684</v>
       </c>
       <c r="O3" t="n">
-        <v>35.32432432432432</v>
+        <v>35.18421052631579</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5378600823045268</v>
+        <v>0.5358717434869739</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.027027027027026</v>
+        <v>8.078947368421053</v>
       </c>
       <c r="R3" t="n">
-        <v>17.86486486486486</v>
+        <v>17.97368421052632</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2720164609053498</v>
+        <v>0.2737474949899799</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="U3" t="n">
-        <v>2.567567567567568</v>
+        <v>2.552631578947369</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03909465020576131</v>
+        <v>0.03887775551102204</v>
       </c>
       <c r="W3" t="n">
-        <v>1.243243243243243</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="X3" t="n">
-        <v>3.135135135135135</v>
+        <v>3.184210526315789</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04773662551440329</v>
+        <v>0.04849699398797595</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.675675675675675</v>
+        <v>7.736842105263158</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.62162162162162</v>
+        <v>22.52631578947368</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3444444444444444</v>
+        <v>0.3430861723446894</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8332058148431523</v>
+        <v>0.8317127898279731</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4493192133131619</v>
+        <v>0.4494875549048317</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3157894736842106</v>
+        <v>0.3195876288659794</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.396551724137931</v>
+        <v>0.3966942148760331</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3393070489844683</v>
+        <v>0.3434579439252336</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.666411629686305</v>
+        <v>1.663425579655946</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6315789473684211</v>
+        <v>0.6391752577319587</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.038824763903463</v>
+        <v>1.050153531218014</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7852760736196319</v>
+        <v>0.7943548387096774</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.036437246963563</v>
+        <v>1.03353057199211</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.704035874439462</v>
+        <v>1.714912280701754</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.439539347408829</v>
+        <v>1.452830188679245</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.664107485604607</v>
+        <v>4.707547169811321</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.103646833013436</v>
+        <v>6.160377358490567</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2794.64</v>
+        <v>2865.440000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>2798.52</v>
+        <v>2869.48</v>
       </c>
       <c r="D4" t="n">
-        <v>114.1674885296514</v>
+        <v>114.167026778371</v>
       </c>
       <c r="E4" t="n">
-        <v>115.6325486328488</v>
+        <v>115.9443522868255</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5506355932203389</v>
+        <v>0.5503508047874536</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1531647789916809</v>
+        <v>0.1516151908639621</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3042813455657493</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2525423728813559</v>
+        <v>0.2513413124226166</v>
       </c>
       <c r="J4" t="n">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="K4" t="n">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="L4" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="M4" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="N4" t="n">
-        <v>1079</v>
+        <v>1104</v>
       </c>
       <c r="O4" t="n">
-        <v>1275</v>
+        <v>1303</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5402542372881356</v>
+        <v>0.5377631035905902</v>
       </c>
       <c r="Q4" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="R4" t="n">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2254237288135593</v>
+        <v>0.224927775484936</v>
       </c>
       <c r="T4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U4" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04067796610169491</v>
+        <v>0.04209657449442839</v>
       </c>
       <c r="W4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="X4" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05466101694915254</v>
+        <v>0.05571605447791993</v>
       </c>
       <c r="Z4" t="n">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="AA4" t="n">
-        <v>924</v>
+        <v>947</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3915254237288135</v>
+        <v>0.3908378043747421</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8462745098039216</v>
+        <v>0.8472755180353031</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4078947368421053</v>
+        <v>0.4055045871559633</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4509803921568628</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4418604651162791</v>
+        <v>0.4370370370370371</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3398268398268398</v>
+        <v>0.3400211193241816</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.692549019607843</v>
+        <v>1.694551036070606</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9019607843137255</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.056980056980057</v>
+        <v>1.05637707948244</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8790786948176583</v>
+        <v>0.8716981132075472</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.103015075376884</v>
+        <v>1.110837438423645</v>
       </c>
       <c r="AM4" t="n">
         <v>1.666666666666667</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.458077709611452</v>
+        <v>1.469758064516129</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.826175869120655</v>
+        <v>4.88508064516129</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.284253578732106</v>
+        <v>6.354838709677419</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.53081081081082</v>
+        <v>75.40631578947369</v>
       </c>
       <c r="C5" t="n">
-        <v>75.63567567567569</v>
+        <v>75.51263157894738</v>
       </c>
       <c r="D5" t="n">
-        <v>114.1674885296514</v>
+        <v>114.167026778371</v>
       </c>
       <c r="E5" t="n">
-        <v>115.6325486328488</v>
+        <v>115.9443522868255</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5506355932203389</v>
+        <v>0.5503508047874536</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1531647789916809</v>
+        <v>0.1516151908639621</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3042813455657493</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2525423728813559</v>
+        <v>0.2513413124226166</v>
       </c>
       <c r="J5" t="n">
-        <v>12.37837837837838</v>
+        <v>12.1578947368421</v>
       </c>
       <c r="K5" t="n">
-        <v>11.86486486486486</v>
+        <v>11.86842105263158</v>
       </c>
       <c r="L5" t="n">
-        <v>9.189189189189189</v>
+        <v>9.210526315789474</v>
       </c>
       <c r="M5" t="n">
-        <v>11.7027027027027</v>
+        <v>11.52631578947368</v>
       </c>
       <c r="N5" t="n">
-        <v>29.16216216216216</v>
+        <v>29.05263157894737</v>
       </c>
       <c r="O5" t="n">
-        <v>34.45945945945946</v>
+        <v>34.28947368421053</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5402542372881356</v>
+        <v>0.5377631035905902</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.864864864864865</v>
+        <v>5.815789473684211</v>
       </c>
       <c r="R5" t="n">
-        <v>14.37837837837838</v>
+        <v>14.3421052631579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2254237288135593</v>
+        <v>0.224927775484936</v>
       </c>
       <c r="T5" t="n">
-        <v>1.162162162162162</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="U5" t="n">
-        <v>2.594594594594595</v>
+        <v>2.684210526315789</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04067796610169492</v>
+        <v>0.04209657449442839</v>
       </c>
       <c r="W5" t="n">
-        <v>1.540540540540541</v>
+        <v>1.552631578947368</v>
       </c>
       <c r="X5" t="n">
-        <v>3.486486486486486</v>
+        <v>3.552631578947369</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05466101694915254</v>
+        <v>0.05571605447791993</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.486486486486486</v>
+        <v>8.473684210526315</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.97297297297297</v>
+        <v>24.92105263157895</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3915254237288135</v>
+        <v>0.3908378043747421</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8462745098039215</v>
+        <v>0.8472755180353032</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4078947368421053</v>
+        <v>0.4055045871559633</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4479166666666666</v>
+        <v>0.4509803921568628</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4418604651162791</v>
+        <v>0.437037037037037</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3398268398268398</v>
+        <v>0.3400211193241816</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.692549019607843</v>
+        <v>1.694551036070606</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.8958333333333333</v>
+        <v>0.9019607843137255</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.056980056980057</v>
+        <v>1.05637707948244</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8790786948176584</v>
+        <v>0.8716981132075471</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.103015075376885</v>
+        <v>1.110837438423645</v>
       </c>
       <c r="AM5" t="n">
         <v>1.666666666666667</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.458077709611452</v>
+        <v>1.469758064516129</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.826175869120655</v>
+        <v>4.88508064516129</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.284253578732106</v>
+        <v>6.354838709677419</v>
       </c>
     </row>
     <row r="7">
@@ -1429,34 +1429,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="D8" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E8" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
         <v>49</v>
       </c>
       <c r="I8" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J8" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="K8" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="L8" t="n">
         <v>31</v>
@@ -1471,19 +1471,19 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>91</v>
+      </c>
+      <c r="R8" t="n">
+        <v>91</v>
+      </c>
+      <c r="S8" t="n">
         <v>102</v>
       </c>
-      <c r="Q8" t="n">
-        <v>90</v>
-      </c>
-      <c r="R8" t="n">
-        <v>90</v>
-      </c>
-      <c r="S8" t="n">
-        <v>101</v>
-      </c>
       <c r="T8" t="n">
-        <v>611</v>
+        <v>628</v>
       </c>
       <c r="U8" t="n">
         <v>63</v>
@@ -1492,28 +1492,28 @@
         <v>61</v>
       </c>
       <c r="W8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="X8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y8" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z8" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="AB8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AC8" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.37</v>
+        <v>0.376</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1534,57 +1534,57 @@
         <v>0.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AL8" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.319</v>
+        <v>0.321</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>1147:28</t>
+          <t>1176:38</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>547.76</v>
+        <v>558.64</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.499</v>
+        <v>0.502</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.515</v>
+        <v>0.517</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.838</v>
+        <v>0.843</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.745</v>
+        <v>2.777</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.029</v>
+        <v>4.078</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.775</v>
+        <v>6.854</v>
       </c>
       <c r="AX8" t="n">
         <v>0.216</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.134</v>
+        <v>0.137</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.284</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="9">
@@ -1905,7 +1905,7 @@
         <v>7</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.154</v>
+        <v>0.155</v>
       </c>
       <c r="AY10" t="n">
         <v>0.013</v>
@@ -2254,22 +2254,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="D13" t="n">
         <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G13" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="H13" t="n">
         <v>56</v>
@@ -2278,10 +2278,10 @@
         <v>69</v>
       </c>
       <c r="J13" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K13" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L13" t="n">
         <v>19</v>
@@ -2290,126 +2290,126 @@
         <v>20</v>
       </c>
       <c r="N13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q13" t="n">
         <v>58</v>
       </c>
-      <c r="Q13" t="n">
-        <v>56</v>
-      </c>
       <c r="R13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S13" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T13" t="n">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="U13" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="V13" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="W13" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="X13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y13" t="n">
         <v>98</v>
       </c>
       <c r="Z13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.79</v>
+        <v>0.784</v>
       </c>
       <c r="AB13" t="n">
         <v>42</v>
       </c>
       <c r="AC13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.457</v>
+        <v>0.452</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
       </c>
       <c r="AF13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH13" t="n">
         <v>7</v>
       </c>
-      <c r="AG13" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>6</v>
-      </c>
       <c r="AI13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="AL13" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.329</v>
+        <v>0.351</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>593:40</t>
+          <t>615:45</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>414.36</v>
+        <v>428.36</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.515</v>
+        <v>0.528</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.55</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.946</v>
+        <v>0.964</v>
       </c>
       <c r="AS13" t="n">
         <v>0.14</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.172</v>
+        <v>0.166</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.931</v>
+        <v>1.933</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.621</v>
+        <v>5.633</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.552</v>
+        <v>7.567</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.317</v>
+        <v>0.316</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="14">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
@@ -2749,67 +2749,67 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I16" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K16" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L16" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M16" t="n">
         <v>20</v>
       </c>
       <c r="N16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R16" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S16" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="T16" t="n">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="U16" t="n">
         <v>30</v>
       </c>
       <c r="V16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W16" t="n">
         <v>19</v>
@@ -2818,22 +2818,22 @@
         <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.764</v>
+        <v>0.767</v>
       </c>
       <c r="AB16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC16" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.486</v>
+        <v>0.474</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -2854,57 +2854,57 @@
         <v>0.533</v>
       </c>
       <c r="AK16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL16" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.366</v>
+        <v>0.378</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>858:12</t>
+          <t>880:39</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>244.68</v>
+        <v>252.56</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.554</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.578</v>
+        <v>0.58</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.891</v>
+        <v>0.899</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.229</v>
+        <v>0.226</v>
       </c>
       <c r="AT16" t="n">
         <v>0.19</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.25</v>
+        <v>1.246</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>3.053</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.25</v>
+        <v>4.298</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.049</v>
+        <v>0.053</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="17">
@@ -2914,22 +2914,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H17" t="n">
         <v>8</v>
@@ -2962,13 +2962,13 @@
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S17" t="n">
         <v>19</v>
       </c>
       <c r="T17" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U17" t="n">
         <v>24</v>
@@ -2995,10 +2995,10 @@
         <v>8</v>
       </c>
       <c r="AC17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.571</v>
+        <v>0.533</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3010,13 +3010,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.55</v>
+        <v>0.571</v>
       </c>
       <c r="AK17" t="n">
         <v>16</v>
@@ -3029,44 +3029,44 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>302:31</t>
+          <t>312:31</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>103.52</v>
+        <v>105.52</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.595</v>
+        <v>0.598</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.614</v>
+        <v>0.617</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.169</v>
+        <v>1.175</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="AU17" t="n">
         <v>1.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.155</v>
+        <v>0.153</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
       <c r="BA17" t="n">
         <v>0.007</v>
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D20" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E20" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3427,25 +3427,25 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J20" t="n">
         <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L20" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M20" t="n">
         <v>12</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3457,19 +3457,19 @@
         <v>18</v>
       </c>
       <c r="R20" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="S20" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="T20" t="n">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="U20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V20" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="W20" t="n">
         <v>14</v>
@@ -3478,22 +3478,22 @@
         <v>10</v>
       </c>
       <c r="Y20" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="Z20" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.867</v>
+        <v>0.873</v>
       </c>
       <c r="AB20" t="n">
         <v>42</v>
       </c>
       <c r="AC20" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.636</v>
+        <v>0.627</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3524,44 +3524,44 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>422:15</t>
+          <t>434:47</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>180.52</v>
+        <v>184.72</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.701</v>
+        <v>0.698</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.726</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.307</v>
+        <v>1.31</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.321</v>
+        <v>0.345</v>
       </c>
       <c r="AU20" t="n">
         <v>0.556</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.611</v>
+        <v>7.722</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.167</v>
+        <v>8.278</v>
       </c>
       <c r="AX20" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="AY20" t="n">
         <v>0.194</v>
       </c>
-      <c r="AY20" t="n">
-        <v>0.197</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>0.143</v>
+        <v>0.147</v>
       </c>
       <c r="BA20" t="n">
         <v>0.008999999999999999</v>
@@ -3904,16 +3904,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -3922,16 +3922,16 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I23" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L23" t="n">
         <v>21</v>
@@ -3952,13 +3952,13 @@
         <v>17</v>
       </c>
       <c r="R23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S23" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T23" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="U23" t="n">
         <v>12</v>
@@ -3973,22 +3973,22 @@
         <v>7</v>
       </c>
       <c r="Y23" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Z23" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.869</v>
+        <v>0.871</v>
       </c>
       <c r="AB23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4019,47 +4019,47 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>330:22</t>
+          <t>338:52</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>147.4</v>
+        <v>150.28</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.623</v>
+        <v>0.62</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.635</v>
+        <v>0.632</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.106</v>
+        <v>1.105</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.129</v>
+        <v>0.126</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.353</v>
+        <v>0.356</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.053</v>
+        <v>1.105</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.368</v>
+        <v>5.474</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.421</v>
+        <v>6.579</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="24">
@@ -4069,16 +4069,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -4087,25 +4087,25 @@
         <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L24" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -4117,19 +4117,19 @@
         <v>16</v>
       </c>
       <c r="R24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="U24" t="n">
         <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W24" t="n">
         <v>7</v>
@@ -4138,22 +4138,22 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Z24" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.861</v>
+        <v>0.805</v>
       </c>
       <c r="AB24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.455</v>
+        <v>0.533</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4184,47 +4184,47 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>187:34</t>
+          <t>204:13</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>69.40000000000001</v>
+        <v>78.72</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.663</v>
+        <v>0.64</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.654</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.052</v>
+        <v>1.042</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.231</v>
+        <v>0.203</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.163</v>
+        <v>0.158</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.062</v>
+        <v>3.562</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.188</v>
+        <v>3.812</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.168</v>
+        <v>0.175</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.164</v>
+        <v>0.162</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.189</v>
+        <v>0.201</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="25">
@@ -4234,43 +4234,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="D25" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E25" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="F25" t="n">
         <v>61</v>
       </c>
       <c r="G25" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I25" t="n">
+        <v>130</v>
+      </c>
+      <c r="J25" t="n">
+        <v>54</v>
+      </c>
+      <c r="K25" t="n">
         <v>125</v>
       </c>
-      <c r="J25" t="n">
-        <v>52</v>
-      </c>
-      <c r="K25" t="n">
-        <v>124</v>
-      </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M25" t="n">
         <v>38</v>
       </c>
       <c r="N25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -4282,111 +4282,111 @@
         <v>72</v>
       </c>
       <c r="R25" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S25" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="T25" t="n">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="U25" t="n">
         <v>88</v>
       </c>
       <c r="V25" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="W25" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="X25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Y25" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="Z25" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AA25" t="n">
         <v>0.866</v>
       </c>
       <c r="AB25" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AC25" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.431</v>
+        <v>0.429</v>
       </c>
       <c r="AE25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.333</v>
+        <v>0.364</v>
       </c>
       <c r="AH25" t="n">
         <v>7</v>
       </c>
       <c r="AI25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.389</v>
+        <v>0.368</v>
       </c>
       <c r="AK25" t="n">
         <v>54</v>
       </c>
       <c r="AL25" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.365</v>
+        <v>0.36</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>872:21</t>
+          <t>897:49</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>539</v>
+        <v>552.2</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.549</v>
+        <v>0.546</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.591</v>
+        <v>0.59</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.022</v>
+        <v>1.023</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.243</v>
+        <v>0.246</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.712</v>
+        <v>0.74</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.63</v>
+        <v>5.781</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.342</v>
+        <v>6.521</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.28</v>
+        <v>0.279</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.162</v>
+        <v>0.159</v>
       </c>
       <c r="BA25" t="n">
         <v>0.054</v>
@@ -4399,22 +4399,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C26" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D26" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E26" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F26" t="n">
         <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H26" t="n">
         <v>53</v>
@@ -4432,7 +4432,7 @@
         <v>64</v>
       </c>
       <c r="M26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N26" t="n">
         <v>28</v>
@@ -4441,19 +4441,19 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q26" t="n">
         <v>26</v>
       </c>
-      <c r="Q26" t="n">
-        <v>25</v>
-      </c>
       <c r="R26" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S26" t="n">
         <v>62</v>
       </c>
       <c r="T26" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="U26" t="n">
         <v>19</v>
@@ -4468,13 +4468,13 @@
         <v>14</v>
       </c>
       <c r="Y26" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Z26" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.886</v>
+        <v>0.887</v>
       </c>
       <c r="AB26" t="n">
         <v>24</v>
@@ -4498,10 +4498,10 @@
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="AK26" t="n">
         <v>23</v>
@@ -4514,47 +4514,47 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>855:59</t>
+          <t>873:31</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>258.68</v>
+        <v>262.68</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.542</v>
+        <v>0.539</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.582</v>
+        <v>0.579</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.048</v>
+        <v>1.039</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.264</v>
+        <v>0.26</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.154</v>
+        <v>1.111</v>
       </c>
       <c r="AV26" t="n">
-        <v>7.731</v>
+        <v>7.556</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.885</v>
+        <v>8.667</v>
       </c>
       <c r="AX26" t="n">
         <v>0.137</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.095</v>
+        <v>0.093</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="27">
@@ -4729,16 +4729,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" t="n">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D28" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E28" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F28" t="n">
         <v>23</v>
@@ -4747,22 +4747,22 @@
         <v>66</v>
       </c>
       <c r="H28" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I28" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J28" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K28" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="L28" t="n">
         <v>58</v>
       </c>
       <c r="M28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N28" t="n">
         <v>27</v>
@@ -4771,49 +4771,49 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q28" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R28" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S28" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="T28" t="n">
-        <v>663</v>
+        <v>678</v>
       </c>
       <c r="U28" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="V28" t="n">
         <v>55</v>
       </c>
       <c r="W28" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="X28" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Y28" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Z28" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.876</v>
+        <v>0.875</v>
       </c>
       <c r="AB28" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AC28" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.485</v>
+        <v>0.493</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -4844,47 +4844,47 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>888:38</t>
+          <t>913:25</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>409.52</v>
+        <v>420.28</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.606</v>
+        <v>0.607</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.673</v>
+        <v>0.671</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.145</v>
+        <v>1.144</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.537</v>
+        <v>0.529</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.082</v>
+        <v>1.097</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.393</v>
+        <v>4.452</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.475</v>
+        <v>5.548</v>
       </c>
       <c r="AX28" t="n">
         <v>0.209</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.074</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ28" t="n">
         <v>0.203</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="29">
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29" t="n">
         <v>65</v>
@@ -4903,13 +4903,13 @@
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H29" t="n">
         <v>16</v>
@@ -4918,13 +4918,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K29" t="n">
         <v>16</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
         <v>6</v>
@@ -4936,16 +4936,16 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R29" t="n">
         <v>33</v>
       </c>
       <c r="S29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T29" t="n">
         <v>45</v>
@@ -4975,10 +4975,10 @@
         <v>6</v>
       </c>
       <c r="AC29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.353</v>
+        <v>0.333</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -5002,54 +5002,54 @@
         <v>10</v>
       </c>
       <c r="AL29" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.2</v>
+        <v>0.196</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>258:17</t>
+          <t>269:07</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>114.92</v>
+        <v>118.92</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.31</v>
+        <v>0.302</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.374</v>
+        <v>0.365</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.547</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.244</v>
+        <v>0.252</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.203</v>
+        <v>0.198</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.929</v>
+        <v>1.867</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.821</v>
+        <v>2.7</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.75</v>
+        <v>4.567</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.047</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="30">
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -5086,10 +5086,10 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L30" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5224,150 +5224,150 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" t="n">
-        <v>3236</v>
+        <v>3327</v>
       </c>
       <c r="D31" t="n">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="E31" t="n">
-        <v>1477</v>
+        <v>1518</v>
       </c>
       <c r="F31" t="n">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G31" t="n">
-        <v>953</v>
+        <v>977</v>
       </c>
       <c r="H31" t="n">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="I31" t="n">
-        <v>785</v>
+        <v>808</v>
       </c>
       <c r="J31" t="n">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="K31" t="n">
-        <v>910</v>
+        <v>938</v>
       </c>
       <c r="L31" t="n">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="M31" t="n">
+        <v>232</v>
+      </c>
+      <c r="N31" t="n">
+        <v>188</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>530</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>478</v>
+      </c>
+      <c r="R31" t="n">
+        <v>720</v>
+      </c>
+      <c r="S31" t="n">
+        <v>812</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4013</v>
+      </c>
+      <c r="U31" t="n">
+        <v>394</v>
+      </c>
+      <c r="V31" t="n">
+        <v>524</v>
+      </c>
+      <c r="W31" t="n">
+        <v>391</v>
+      </c>
+      <c r="X31" t="n">
         <v>228</v>
       </c>
-      <c r="N31" t="n">
-        <v>182</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>521</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>470</v>
-      </c>
-      <c r="R31" t="n">
-        <v>702</v>
-      </c>
-      <c r="S31" t="n">
-        <v>791</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3899</v>
-      </c>
-      <c r="U31" t="n">
-        <v>384</v>
-      </c>
-      <c r="V31" t="n">
-        <v>512</v>
-      </c>
-      <c r="W31" t="n">
-        <v>380</v>
-      </c>
-      <c r="X31" t="n">
-        <v>223</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1089</v>
+        <v>1112</v>
       </c>
       <c r="Z31" t="n">
-        <v>1307</v>
+        <v>1337</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.833</v>
+        <v>0.832</v>
       </c>
       <c r="AB31" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="AC31" t="n">
-        <v>661</v>
+        <v>683</v>
       </c>
       <c r="AD31" t="n">
         <v>0.449</v>
       </c>
       <c r="AE31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF31" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.316</v>
+        <v>0.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AI31" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AJ31" t="n">
         <v>0.397</v>
       </c>
       <c r="AK31" t="n">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="AL31" t="n">
-        <v>837</v>
+        <v>856</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.339</v>
+        <v>0.343</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>7475:00</t>
+          <t>7675:00</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>3296.4</v>
+        <v>3380.52</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.545</v>
+        <v>0.547</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.583</v>
+        <v>0.584</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.982</v>
+        <v>0.984</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.158</v>
+        <v>0.157</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.241</v>
+        <v>0.24</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.44</v>
+        <v>1.453</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.664</v>
+        <v>4.708</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.104</v>
+        <v>6.16</v>
       </c>
       <c r="AX31" t="n">
         <v>0.2</v>
@@ -5376,7 +5376,7 @@
         <v>0.075</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.139</v>
+        <v>0.14</v>
       </c>
       <c r="BA31" t="n">
         <v>0</v>
@@ -5389,156 +5389,156 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C32" t="n">
-        <v>3195</v>
+        <v>3276</v>
       </c>
       <c r="D32" t="n">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="E32" t="n">
-        <v>1307</v>
+        <v>1341</v>
       </c>
       <c r="F32" t="n">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="G32" t="n">
-        <v>1053</v>
+        <v>1082</v>
       </c>
       <c r="H32" t="n">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="I32" t="n">
-        <v>781</v>
+        <v>801</v>
       </c>
       <c r="J32" t="n">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="K32" t="n">
-        <v>818</v>
+        <v>842</v>
       </c>
       <c r="L32" t="n">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="M32" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="N32" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="Q32" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="R32" t="n">
-        <v>713</v>
+        <v>734</v>
       </c>
       <c r="S32" t="n">
-        <v>774</v>
+        <v>792</v>
       </c>
       <c r="T32" t="n">
-        <v>3743</v>
+        <v>3834</v>
       </c>
       <c r="U32" t="n">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="V32" t="n">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="W32" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="X32" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="Y32" t="n">
-        <v>1079</v>
+        <v>1104</v>
       </c>
       <c r="Z32" t="n">
-        <v>1275</v>
+        <v>1303</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.846</v>
+        <v>0.847</v>
       </c>
       <c r="AB32" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AC32" t="n">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.408</v>
+        <v>0.406</v>
       </c>
       <c r="AE32" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AF32" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.448</v>
+        <v>0.451</v>
       </c>
       <c r="AH32" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AI32" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.442</v>
+        <v>0.437</v>
       </c>
       <c r="AK32" t="n">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="AL32" t="n">
-        <v>924</v>
+        <v>947</v>
       </c>
       <c r="AM32" t="n">
         <v>0.34</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>7475:00</t>
+          <t>7675:00</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>3192.64</v>
+        <v>3271.44</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.551</v>
+        <v>0.55</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.591</v>
+        <v>0.59</v>
       </c>
       <c r="AR32" t="n">
         <v>1.001</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.253</v>
+        <v>0.251</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.458</v>
+        <v>1.47</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.826</v>
+        <v>4.885</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.284</v>
+        <v>6.355</v>
       </c>
       <c r="AX32" t="n">
         <v>0.2</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="AZ32" t="n">
         <v>0.125</v>
@@ -5613,162 +5613,162 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C34" t="n">
-        <v>12.405</v>
+        <v>12.395</v>
       </c>
       <c r="D34" t="n">
-        <v>3.027</v>
+        <v>3.026</v>
       </c>
       <c r="E34" t="n">
-        <v>5.838</v>
+        <v>5.789</v>
       </c>
       <c r="F34" t="n">
-        <v>1.676</v>
+        <v>1.684</v>
       </c>
       <c r="G34" t="n">
-        <v>5.27</v>
+        <v>5.263</v>
       </c>
       <c r="H34" t="n">
-        <v>1.324</v>
+        <v>1.289</v>
       </c>
       <c r="I34" t="n">
-        <v>2.135</v>
+        <v>2.132</v>
       </c>
       <c r="J34" t="n">
-        <v>7.568</v>
+        <v>7.526</v>
       </c>
       <c r="K34" t="n">
-        <v>3.649</v>
+        <v>3.711</v>
       </c>
       <c r="L34" t="n">
-        <v>0.838</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>1.027</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>0.703</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.757</v>
+        <v>2.711</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.432</v>
+        <v>2.395</v>
       </c>
       <c r="R34" t="n">
-        <v>2.432</v>
+        <v>2.395</v>
       </c>
       <c r="S34" t="n">
-        <v>2.73</v>
+        <v>2.684</v>
       </c>
       <c r="T34" t="n">
-        <v>611</v>
+        <v>628</v>
       </c>
       <c r="U34" t="n">
-        <v>1.703</v>
+        <v>1.658</v>
       </c>
       <c r="V34" t="n">
-        <v>1.649</v>
+        <v>1.605</v>
       </c>
       <c r="W34" t="n">
-        <v>1.568</v>
+        <v>1.579</v>
       </c>
       <c r="X34" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.297</v>
+        <v>3.263</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.243</v>
+        <v>4.211</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.486</v>
+        <v>2.447</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.37</v>
+        <v>0.376</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.432</v>
+        <v>0.421</v>
       </c>
       <c r="AG34" t="n">
         <v>0.312</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.27</v>
+        <v>0.263</v>
       </c>
       <c r="AJ34" t="n">
         <v>0.3</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.595</v>
+        <v>1.605</v>
       </c>
       <c r="AL34" t="n">
         <v>5</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.319</v>
+        <v>0.321</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>31:00</t>
+          <t>30:57</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>14.804</v>
+        <v>14.701</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.499</v>
+        <v>0.502</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.515</v>
+        <v>0.517</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.838</v>
+        <v>0.843</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.745</v>
+        <v>2.777</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.029</v>
+        <v>4.078</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.775</v>
+        <v>6.854</v>
       </c>
       <c r="AX34" t="n">
         <v>0.216</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.134</v>
+        <v>0.137</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.284</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="35">
@@ -6089,7 +6089,7 @@
         <v>7</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.154</v>
+        <v>0.155</v>
       </c>
       <c r="AY36" t="n">
         <v>0.013</v>
@@ -6438,162 +6438,162 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C39" t="n">
-        <v>13.067</v>
+        <v>13.323</v>
       </c>
       <c r="D39" t="n">
-        <v>2.9</v>
+        <v>2.806</v>
       </c>
       <c r="E39" t="n">
-        <v>5.567</v>
+        <v>5.484</v>
       </c>
       <c r="F39" t="n">
-        <v>1.8</v>
+        <v>1.968</v>
       </c>
       <c r="G39" t="n">
-        <v>5.3</v>
+        <v>5.419</v>
       </c>
       <c r="H39" t="n">
-        <v>1.867</v>
+        <v>1.806</v>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>2.226</v>
       </c>
       <c r="J39" t="n">
-        <v>3.733</v>
+        <v>3.742</v>
       </c>
       <c r="K39" t="n">
-        <v>1.5</v>
+        <v>1.516</v>
       </c>
       <c r="L39" t="n">
-        <v>0.633</v>
+        <v>0.613</v>
       </c>
       <c r="M39" t="n">
-        <v>0.667</v>
+        <v>0.645</v>
       </c>
       <c r="N39" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.871</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="T39" t="n">
+        <v>368</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>3.161</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>4.032</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>0.5</v>
       </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.933</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.867</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.367</v>
-      </c>
-      <c r="T39" t="n">
-        <v>346</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.133</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.467</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.467</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.067</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0.462</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.6</v>
+        <v>1.742</v>
       </c>
       <c r="AL39" t="n">
-        <v>4.867</v>
+        <v>4.968</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.329</v>
+        <v>0.351</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>13.812</v>
+        <v>13.818</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.515</v>
+        <v>0.528</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.55</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.946</v>
+        <v>0.964</v>
       </c>
       <c r="AS39" t="n">
         <v>0.14</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.172</v>
+        <v>0.166</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.931</v>
+        <v>1.933</v>
       </c>
       <c r="AV39" t="n">
-        <v>5.621</v>
+        <v>5.633</v>
       </c>
       <c r="AW39" t="n">
-        <v>7.552</v>
+        <v>7.567</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.317</v>
+        <v>0.316</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="AZ39" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="40">
@@ -6603,88 +6603,88 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C40" t="n">
-        <v>1.833</v>
+        <v>1.774</v>
       </c>
       <c r="D40" t="n">
-        <v>0.533</v>
+        <v>0.516</v>
       </c>
       <c r="E40" t="n">
-        <v>0.867</v>
+        <v>0.839</v>
       </c>
       <c r="F40" t="n">
-        <v>0.167</v>
+        <v>0.161</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4</v>
+        <v>0.387</v>
       </c>
       <c r="H40" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="I40" t="n">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="K40" t="n">
-        <v>0.9</v>
+        <v>0.871</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="N40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.167</v>
+        <v>0.161</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.167</v>
+        <v>0.161</v>
       </c>
       <c r="R40" t="n">
-        <v>1.2</v>
+        <v>1.161</v>
       </c>
       <c r="S40" t="n">
-        <v>0.5</v>
+        <v>0.484</v>
       </c>
       <c r="T40" t="n">
         <v>73</v>
       </c>
       <c r="U40" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="V40" t="n">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="W40" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="X40" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.733</v>
+        <v>0.71</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.867</v>
+        <v>0.839</v>
       </c>
       <c r="AA40" t="n">
         <v>0.846</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.2</v>
+        <v>0.194</v>
       </c>
       <c r="AD40" t="n">
         <v>0.333</v>
@@ -6693,7 +6693,7 @@
         <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -6702,27 +6702,27 @@
         <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="AJ40" t="n">
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.167</v>
+        <v>0.161</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.333</v>
+        <v>0.323</v>
       </c>
       <c r="AM40" t="n">
         <v>0.5</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>1.595</v>
+        <v>1.543</v>
       </c>
       <c r="AP40" t="n">
         <v>0.618</v>
@@ -6758,7 +6758,7 @@
         <v>0.103</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -6933,162 +6933,162 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C42" t="n">
-        <v>5.892</v>
+        <v>5.974</v>
       </c>
       <c r="D42" t="n">
-        <v>1.135</v>
+        <v>1.132</v>
       </c>
       <c r="E42" t="n">
-        <v>2.216</v>
+        <v>2.237</v>
       </c>
       <c r="F42" t="n">
-        <v>0.919</v>
+        <v>0.947</v>
       </c>
       <c r="G42" t="n">
-        <v>2.324</v>
+        <v>2.342</v>
       </c>
       <c r="H42" t="n">
-        <v>0.865</v>
+        <v>0.868</v>
       </c>
       <c r="I42" t="n">
-        <v>1.27</v>
+        <v>1.289</v>
       </c>
       <c r="J42" t="n">
-        <v>1.892</v>
+        <v>1.868</v>
       </c>
       <c r="K42" t="n">
-        <v>2.351</v>
+        <v>2.368</v>
       </c>
       <c r="L42" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.447</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.289</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.658</v>
+      </c>
+      <c r="T42" t="n">
+        <v>276</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.921</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AC42" t="n">
         <v>1</v>
       </c>
-      <c r="M42" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.514</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.459</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1.622</v>
-      </c>
-      <c r="T42" t="n">
-        <v>263</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.486</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.946</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0.946</v>
-      </c>
       <c r="AD42" t="n">
-        <v>0.486</v>
+        <v>0.474</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.189</v>
+        <v>0.184</v>
       </c>
       <c r="AG42" t="n">
         <v>0.286</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.216</v>
+        <v>0.211</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.405</v>
+        <v>0.395</v>
       </c>
       <c r="AJ42" t="n">
         <v>0.533</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.703</v>
+        <v>0.737</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.919</v>
+        <v>1.947</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.366</v>
+        <v>0.378</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>23:11</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>6.613</v>
+        <v>6.646</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.554</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.578</v>
+        <v>0.58</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.891</v>
+        <v>0.899</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.229</v>
+        <v>0.226</v>
       </c>
       <c r="AT42" t="n">
         <v>0.19</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.25</v>
+        <v>1.246</v>
       </c>
       <c r="AV42" t="n">
-        <v>3</v>
+        <v>3.053</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.25</v>
+        <v>4.298</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.049</v>
+        <v>0.053</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="43">
@@ -7098,159 +7098,159 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" t="n">
-        <v>5.042</v>
+        <v>4.96</v>
       </c>
       <c r="D43" t="n">
-        <v>0.667</v>
+        <v>0.64</v>
       </c>
       <c r="E43" t="n">
-        <v>1.417</v>
+        <v>1.4</v>
       </c>
       <c r="F43" t="n">
-        <v>1.125</v>
+        <v>1.12</v>
       </c>
       <c r="G43" t="n">
-        <v>2.542</v>
+        <v>2.48</v>
       </c>
       <c r="H43" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="I43" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="J43" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="K43" t="n">
-        <v>1.042</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0.792</v>
+        <v>0.76</v>
       </c>
       <c r="M43" t="n">
-        <v>0.417</v>
+        <v>0.4</v>
       </c>
       <c r="N43" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.208</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.167</v>
+        <v>0.16</v>
       </c>
       <c r="R43" t="n">
-        <v>1.208</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>0.792</v>
+        <v>0.76</v>
       </c>
       <c r="T43" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="V43" t="n">
-        <v>0.667</v>
+        <v>0.64</v>
       </c>
       <c r="W43" t="n">
-        <v>0.875</v>
+        <v>0.84</v>
       </c>
       <c r="X43" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.667</v>
+        <v>0.64</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.125</v>
+        <v>1.08</v>
       </c>
       <c r="AA43" t="n">
         <v>0.593</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.583</v>
+        <v>0.6</v>
       </c>
       <c r="AD43" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>0.571</v>
       </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.55</v>
-      </c>
       <c r="AK43" t="n">
-        <v>0.667</v>
+        <v>0.64</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.708</v>
+        <v>1.64</v>
       </c>
       <c r="AM43" t="n">
         <v>0.39</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>4.313</v>
+        <v>4.221</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.595</v>
+        <v>0.598</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.614</v>
+        <v>0.617</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.169</v>
+        <v>1.175</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="AU43" t="n">
         <v>1.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="AW43" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.155</v>
+        <v>0.153</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
       <c r="BA43" t="n">
         <v>0.011</v>
@@ -7593,16 +7593,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C46" t="n">
-        <v>7.375</v>
+        <v>7.333</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2.939</v>
       </c>
       <c r="E46" t="n">
-        <v>4.281</v>
+        <v>4.212</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -7611,79 +7611,79 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.375</v>
+        <v>1.455</v>
       </c>
       <c r="I46" t="n">
-        <v>1.812</v>
+        <v>1.909</v>
       </c>
       <c r="J46" t="n">
-        <v>0.312</v>
+        <v>0.303</v>
       </c>
       <c r="K46" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="L46" t="n">
-        <v>2.281</v>
+        <v>2.242</v>
       </c>
       <c r="M46" t="n">
-        <v>0.375</v>
+        <v>0.364</v>
       </c>
       <c r="N46" t="n">
-        <v>0.625</v>
+        <v>0.636</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="R46" t="n">
-        <v>2.156</v>
+        <v>2.152</v>
       </c>
       <c r="S46" t="n">
-        <v>1.688</v>
+        <v>1.727</v>
       </c>
       <c r="T46" t="n">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="U46" t="n">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="V46" t="n">
-        <v>2.688</v>
+        <v>2.697</v>
       </c>
       <c r="W46" t="n">
-        <v>0.438</v>
+        <v>0.424</v>
       </c>
       <c r="X46" t="n">
-        <v>0.312</v>
+        <v>0.303</v>
       </c>
       <c r="Y46" t="n">
-        <v>3.062</v>
+        <v>3.121</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.531</v>
+        <v>3.576</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.867</v>
+        <v>0.873</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.312</v>
+        <v>1.273</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.062</v>
+        <v>2.03</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.636</v>
+        <v>0.627</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -7708,44 +7708,44 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>5.641</v>
+        <v>5.598</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.701</v>
+        <v>0.698</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.726</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.307</v>
+        <v>1.31</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.1</v>
+        <v>0.097</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.321</v>
+        <v>0.345</v>
       </c>
       <c r="AU46" t="n">
         <v>0.556</v>
       </c>
       <c r="AV46" t="n">
-        <v>7.611</v>
+        <v>7.722</v>
       </c>
       <c r="AW46" t="n">
-        <v>8.167</v>
+        <v>8.278</v>
       </c>
       <c r="AX46" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="AY46" t="n">
         <v>0.194</v>
       </c>
-      <c r="AY46" t="n">
-        <v>0.197</v>
-      </c>
       <c r="AZ46" t="n">
-        <v>0.143</v>
+        <v>0.147</v>
       </c>
       <c r="BA46" t="n">
         <v>0.011</v>
@@ -8088,91 +8088,91 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C49" t="n">
-        <v>5.621</v>
+        <v>5.533</v>
       </c>
       <c r="D49" t="n">
-        <v>1.931</v>
+        <v>1.9</v>
       </c>
       <c r="E49" t="n">
-        <v>3.034</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>0.172</v>
+        <v>0.167</v>
       </c>
       <c r="G49" t="n">
-        <v>0.483</v>
+        <v>0.467</v>
       </c>
       <c r="H49" t="n">
-        <v>1.241</v>
+        <v>1.233</v>
       </c>
       <c r="I49" t="n">
-        <v>2.069</v>
+        <v>2.067</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="K49" t="n">
-        <v>0.931</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>0.724</v>
+        <v>0.7</v>
       </c>
       <c r="M49" t="n">
-        <v>0.276</v>
+        <v>0.267</v>
       </c>
       <c r="N49" t="n">
-        <v>0.138</v>
+        <v>0.133</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.655</v>
+        <v>0.633</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.586</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="R49" t="n">
-        <v>0.931</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="S49" t="n">
-        <v>2.552</v>
+        <v>2.5</v>
       </c>
       <c r="T49" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="U49" t="n">
-        <v>0.414</v>
+        <v>0.4</v>
       </c>
       <c r="V49" t="n">
-        <v>1.138</v>
+        <v>1.1</v>
       </c>
       <c r="W49" t="n">
-        <v>0.414</v>
+        <v>0.4</v>
       </c>
       <c r="X49" t="n">
-        <v>0.241</v>
+        <v>0.233</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.517</v>
+        <v>2.467</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.897</v>
+        <v>2.833</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.869</v>
+        <v>0.871</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.655</v>
+        <v>0.667</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.379</v>
+        <v>1.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8187,60 +8187,60 @@
         <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="AJ49" t="n">
         <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.172</v>
+        <v>0.167</v>
       </c>
       <c r="AL49" t="n">
-        <v>0.448</v>
+        <v>0.433</v>
       </c>
       <c r="AM49" t="n">
         <v>0.385</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>5.083</v>
+        <v>5.009</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.623</v>
+        <v>0.62</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.635</v>
+        <v>0.632</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.106</v>
+        <v>1.105</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.129</v>
+        <v>0.126</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.353</v>
+        <v>0.356</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.053</v>
+        <v>1.105</v>
       </c>
       <c r="AV49" t="n">
-        <v>5.368</v>
+        <v>5.474</v>
       </c>
       <c r="AW49" t="n">
-        <v>6.421</v>
+        <v>6.579</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="BA49" t="n">
         <v>0.024</v>
@@ -8253,106 +8253,106 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>5.615</v>
+        <v>5.857</v>
       </c>
       <c r="D50" t="n">
-        <v>2.154</v>
+        <v>2.286</v>
       </c>
       <c r="E50" t="n">
-        <v>3.385</v>
+        <v>3.714</v>
       </c>
       <c r="F50" t="n">
-        <v>0.231</v>
+        <v>0.214</v>
       </c>
       <c r="G50" t="n">
-        <v>0.385</v>
+        <v>0.357</v>
       </c>
       <c r="H50" t="n">
-        <v>0.615</v>
+        <v>0.643</v>
       </c>
       <c r="I50" t="n">
-        <v>0.769</v>
+        <v>0.929</v>
       </c>
       <c r="J50" t="n">
-        <v>0.154</v>
+        <v>0.286</v>
       </c>
       <c r="K50" t="n">
-        <v>2.385</v>
+        <v>2.571</v>
       </c>
       <c r="L50" t="n">
-        <v>2.077</v>
+        <v>2.071</v>
       </c>
       <c r="M50" t="n">
-        <v>0.308</v>
+        <v>0.429</v>
       </c>
       <c r="N50" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.231</v>
+        <v>1.143</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.231</v>
+        <v>1.143</v>
       </c>
       <c r="R50" t="n">
-        <v>1.154</v>
+        <v>1.214</v>
       </c>
       <c r="S50" t="n">
-        <v>1.385</v>
+        <v>1.429</v>
       </c>
       <c r="T50" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="U50" t="n">
-        <v>0.308</v>
+        <v>0.286</v>
       </c>
       <c r="V50" t="n">
-        <v>1.154</v>
+        <v>1.214</v>
       </c>
       <c r="W50" t="n">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="X50" t="n">
-        <v>0.385</v>
+        <v>0.357</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.385</v>
+        <v>2.357</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.769</v>
+        <v>2.929</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.861</v>
+        <v>0.805</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.385</v>
+        <v>0.571</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.846</v>
+        <v>1.071</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.455</v>
+        <v>0.533</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.385</v>
+        <v>0.357</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.231</v>
+        <v>0.214</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.385</v>
+        <v>0.357</v>
       </c>
       <c r="AJ50" t="n">
         <v>0.6</v>
@@ -8368,47 +8368,47 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>5.338</v>
+        <v>5.623</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.663</v>
+        <v>0.64</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.654</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.052</v>
+        <v>1.042</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.231</v>
+        <v>0.203</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.163</v>
+        <v>0.158</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.062</v>
+        <v>3.562</v>
       </c>
       <c r="AW50" t="n">
-        <v>3.187</v>
+        <v>3.812</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.168</v>
+        <v>0.175</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.164</v>
+        <v>0.162</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.189</v>
+        <v>0.201</v>
       </c>
       <c r="BA50" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="51">
@@ -8418,162 +8418,162 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C51" t="n">
-        <v>17.219</v>
+        <v>17.121</v>
       </c>
       <c r="D51" t="n">
-        <v>4.188</v>
+        <v>4.212</v>
       </c>
       <c r="E51" t="n">
-        <v>7.656</v>
+        <v>7.667</v>
       </c>
       <c r="F51" t="n">
-        <v>1.906</v>
+        <v>1.848</v>
       </c>
       <c r="G51" t="n">
-        <v>5.188</v>
+        <v>5.121</v>
       </c>
       <c r="H51" t="n">
-        <v>3.125</v>
+        <v>3.152</v>
       </c>
       <c r="I51" t="n">
-        <v>3.906</v>
+        <v>3.939</v>
       </c>
       <c r="J51" t="n">
-        <v>1.625</v>
+        <v>1.636</v>
       </c>
       <c r="K51" t="n">
-        <v>3.875</v>
+        <v>3.788</v>
       </c>
       <c r="L51" t="n">
-        <v>0.625</v>
+        <v>0.667</v>
       </c>
       <c r="M51" t="n">
-        <v>1.188</v>
+        <v>1.152</v>
       </c>
       <c r="N51" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.281</v>
+        <v>2.212</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.25</v>
+        <v>2.182</v>
       </c>
       <c r="R51" t="n">
-        <v>1.719</v>
+        <v>1.697</v>
       </c>
       <c r="S51" t="n">
-        <v>3.531</v>
+        <v>3.545</v>
       </c>
       <c r="T51" t="n">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="U51" t="n">
-        <v>2.75</v>
+        <v>2.667</v>
       </c>
       <c r="V51" t="n">
-        <v>1.75</v>
+        <v>1.788</v>
       </c>
       <c r="W51" t="n">
-        <v>1.844</v>
+        <v>1.848</v>
       </c>
       <c r="X51" t="n">
-        <v>1.031</v>
+        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
-        <v>5.438</v>
+        <v>5.485</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.281</v>
+        <v>6.333</v>
       </c>
       <c r="AA51" t="n">
         <v>0.866</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.844</v>
+        <v>3.818</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.431</v>
+        <v>0.429</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.219</v>
+        <v>0.242</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.656</v>
+        <v>0.667</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.333</v>
+        <v>0.364</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.219</v>
+        <v>0.212</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.576</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.389</v>
+        <v>0.368</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.688</v>
+        <v>1.636</v>
       </c>
       <c r="AL51" t="n">
-        <v>4.625</v>
+        <v>4.545</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.365</v>
+        <v>0.36</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>27:15</t>
+          <t>27:12</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>16.844</v>
+        <v>16.733</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.549</v>
+        <v>0.546</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.591</v>
+        <v>0.59</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.022</v>
+        <v>1.023</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="AT51" t="n">
-        <v>0.243</v>
+        <v>0.246</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.712</v>
+        <v>0.74</v>
       </c>
       <c r="AV51" t="n">
-        <v>5.63</v>
+        <v>5.781</v>
       </c>
       <c r="AW51" t="n">
-        <v>6.342</v>
+        <v>6.521</v>
       </c>
       <c r="AX51" t="n">
-        <v>0.28</v>
+        <v>0.279</v>
       </c>
       <c r="AY51" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.162</v>
+        <v>0.159</v>
       </c>
       <c r="BA51" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="52">
@@ -8583,162 +8583,162 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C52" t="n">
-        <v>7.324</v>
+        <v>7.184</v>
       </c>
       <c r="D52" t="n">
-        <v>1.811</v>
+        <v>1.789</v>
       </c>
       <c r="E52" t="n">
-        <v>3.378</v>
+        <v>3.316</v>
       </c>
       <c r="F52" t="n">
-        <v>0.757</v>
+        <v>0.737</v>
       </c>
       <c r="G52" t="n">
-        <v>2.054</v>
+        <v>2.053</v>
       </c>
       <c r="H52" t="n">
-        <v>1.432</v>
+        <v>1.395</v>
       </c>
       <c r="I52" t="n">
-        <v>1.946</v>
+        <v>1.895</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.789</v>
       </c>
       <c r="K52" t="n">
-        <v>1.919</v>
+        <v>1.868</v>
       </c>
       <c r="L52" t="n">
-        <v>1.73</v>
+        <v>1.684</v>
       </c>
       <c r="M52" t="n">
-        <v>0.486</v>
+        <v>0.5</v>
       </c>
       <c r="N52" t="n">
-        <v>0.757</v>
+        <v>0.737</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0.703</v>
+        <v>0.711</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.676</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="R52" t="n">
-        <v>1.622</v>
+        <v>1.632</v>
       </c>
       <c r="S52" t="n">
-        <v>1.676</v>
+        <v>1.632</v>
       </c>
       <c r="T52" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="U52" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="V52" t="n">
-        <v>1.568</v>
+        <v>1.526</v>
       </c>
       <c r="W52" t="n">
-        <v>0.73</v>
+        <v>0.711</v>
       </c>
       <c r="X52" t="n">
-        <v>0.378</v>
+        <v>0.368</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.514</v>
+        <v>2.474</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.838</v>
+        <v>2.789</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.886</v>
+        <v>0.887</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.649</v>
+        <v>0.632</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.757</v>
+        <v>1.711</v>
       </c>
       <c r="AD52" t="n">
         <v>0.369</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.216</v>
+        <v>0.211</v>
       </c>
       <c r="AG52" t="n">
         <v>0.375</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.514</v>
+        <v>0.553</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="AK52" t="n">
-        <v>0.622</v>
+        <v>0.605</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.541</v>
+        <v>1.5</v>
       </c>
       <c r="AM52" t="n">
         <v>0.404</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>6.991</v>
+        <v>6.913</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.542</v>
+        <v>0.539</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.582</v>
+        <v>0.579</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.048</v>
+        <v>1.039</v>
       </c>
       <c r="AS52" t="n">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="AT52" t="n">
-        <v>0.264</v>
+        <v>0.26</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.154</v>
+        <v>1.111</v>
       </c>
       <c r="AV52" t="n">
-        <v>7.731</v>
+        <v>7.556</v>
       </c>
       <c r="AW52" t="n">
-        <v>8.885</v>
+        <v>8.667</v>
       </c>
       <c r="AX52" t="n">
         <v>0.137</v>
       </c>
       <c r="AY52" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0.095</v>
+        <v>0.093</v>
       </c>
       <c r="BA52" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="53">
@@ -8913,97 +8913,97 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C54" t="n">
-        <v>13.794</v>
+        <v>13.743</v>
       </c>
       <c r="D54" t="n">
-        <v>3.765</v>
+        <v>3.8</v>
       </c>
       <c r="E54" t="n">
-        <v>5.941</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>0.676</v>
+        <v>0.657</v>
       </c>
       <c r="G54" t="n">
-        <v>1.941</v>
+        <v>1.886</v>
       </c>
       <c r="H54" t="n">
-        <v>4.235</v>
+        <v>4.171</v>
       </c>
       <c r="I54" t="n">
-        <v>5.382</v>
+        <v>5.343</v>
       </c>
       <c r="J54" t="n">
-        <v>1.941</v>
+        <v>1.943</v>
       </c>
       <c r="K54" t="n">
-        <v>4.647</v>
+        <v>4.629</v>
       </c>
       <c r="L54" t="n">
-        <v>1.706</v>
+        <v>1.657</v>
       </c>
       <c r="M54" t="n">
         <v>0.971</v>
       </c>
       <c r="N54" t="n">
-        <v>0.794</v>
+        <v>0.771</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>1.794</v>
+        <v>1.771</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.647</v>
+        <v>1.629</v>
       </c>
       <c r="R54" t="n">
-        <v>2.206</v>
+        <v>2.2</v>
       </c>
       <c r="S54" t="n">
-        <v>4.235</v>
+        <v>4.229</v>
       </c>
       <c r="T54" t="n">
-        <v>663</v>
+        <v>678</v>
       </c>
       <c r="U54" t="n">
-        <v>1.824</v>
+        <v>1.857</v>
       </c>
       <c r="V54" t="n">
-        <v>1.618</v>
+        <v>1.571</v>
       </c>
       <c r="W54" t="n">
-        <v>2.647</v>
+        <v>2.686</v>
       </c>
       <c r="X54" t="n">
-        <v>1.882</v>
+        <v>1.886</v>
       </c>
       <c r="Y54" t="n">
-        <v>6.853</v>
+        <v>6.771</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.824</v>
+        <v>7.743</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.876</v>
+        <v>0.875</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.971</v>
+        <v>1.029</v>
       </c>
       <c r="AC54" t="n">
-        <v>2</v>
+        <v>2.086</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.485</v>
+        <v>0.493</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.176</v>
+        <v>0.171</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.353</v>
+        <v>0.343</v>
       </c>
       <c r="AG54" t="n">
         <v>0.5</v>
@@ -9012,57 +9012,57 @@
         <v>0.029</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="AJ54" t="n">
         <v>0.5</v>
       </c>
       <c r="AK54" t="n">
-        <v>0.647</v>
+        <v>0.629</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.882</v>
+        <v>1.829</v>
       </c>
       <c r="AM54" t="n">
         <v>0.344</v>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>26:08</t>
+          <t>26:05</t>
         </is>
       </c>
       <c r="AO54" t="n">
-        <v>12.045</v>
+        <v>12.008</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.606</v>
+        <v>0.607</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.673</v>
+        <v>0.671</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.145</v>
+        <v>1.144</v>
       </c>
       <c r="AS54" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.537</v>
+        <v>0.529</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.082</v>
+        <v>1.097</v>
       </c>
       <c r="AV54" t="n">
-        <v>4.393</v>
+        <v>4.452</v>
       </c>
       <c r="AW54" t="n">
-        <v>5.475</v>
+        <v>5.548</v>
       </c>
       <c r="AX54" t="n">
         <v>0.209</v>
       </c>
       <c r="AY54" t="n">
-        <v>0.074</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ54" t="n">
         <v>0.203</v>
@@ -9078,159 +9078,159 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C55" t="n">
-        <v>2.321</v>
+        <v>2.241</v>
       </c>
       <c r="D55" t="n">
-        <v>0.286</v>
+        <v>0.276</v>
       </c>
       <c r="E55" t="n">
-        <v>0.964</v>
+        <v>0.966</v>
       </c>
       <c r="F55" t="n">
-        <v>0.393</v>
+        <v>0.379</v>
       </c>
       <c r="G55" t="n">
-        <v>1.857</v>
+        <v>1.828</v>
       </c>
       <c r="H55" t="n">
-        <v>0.571</v>
+        <v>0.552</v>
       </c>
       <c r="I55" t="n">
-        <v>0.643</v>
+        <v>0.621</v>
       </c>
       <c r="J55" t="n">
-        <v>1.929</v>
+        <v>1.931</v>
       </c>
       <c r="K55" t="n">
-        <v>0.571</v>
+        <v>0.552</v>
       </c>
       <c r="L55" t="n">
-        <v>0.107</v>
+        <v>0.138</v>
       </c>
       <c r="M55" t="n">
-        <v>0.214</v>
+        <v>0.207</v>
       </c>
       <c r="N55" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>1.034</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>1.034</v>
       </c>
       <c r="R55" t="n">
-        <v>1.179</v>
+        <v>1.138</v>
       </c>
       <c r="S55" t="n">
-        <v>0.786</v>
+        <v>0.793</v>
       </c>
       <c r="T55" t="n">
         <v>45</v>
       </c>
       <c r="U55" t="n">
-        <v>0.393</v>
+        <v>0.379</v>
       </c>
       <c r="V55" t="n">
-        <v>0.464</v>
+        <v>0.448</v>
       </c>
       <c r="W55" t="n">
-        <v>0.321</v>
+        <v>0.31</v>
       </c>
       <c r="X55" t="n">
-        <v>0.25</v>
+        <v>0.241</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.607</v>
+        <v>0.586</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.821</v>
+        <v>0.793</v>
       </c>
       <c r="AA55" t="n">
         <v>0.739</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.214</v>
+        <v>0.207</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.607</v>
+        <v>0.621</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.353</v>
+        <v>0.333</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.107</v>
+        <v>0.103</v>
       </c>
       <c r="AG55" t="n">
         <v>0.333</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AJ55" t="n">
         <v>0.5</v>
       </c>
       <c r="AK55" t="n">
-        <v>0.357</v>
+        <v>0.345</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.786</v>
+        <v>1.759</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.2</v>
+        <v>0.196</v>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>4.104</v>
+        <v>4.101</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.31</v>
+        <v>0.302</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.374</v>
+        <v>0.365</v>
       </c>
       <c r="AR55" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.547</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.244</v>
+        <v>0.252</v>
       </c>
       <c r="AT55" t="n">
-        <v>0.203</v>
+        <v>0.198</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.929</v>
+        <v>1.867</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.821</v>
+        <v>2.7</v>
       </c>
       <c r="AW55" t="n">
-        <v>4.75</v>
+        <v>4.567</v>
       </c>
       <c r="AX55" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="AY55" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="BA55" t="n">
         <v>0.063</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -9270,10 +9270,10 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>1.865</v>
+        <v>1.895</v>
       </c>
       <c r="L56" t="n">
-        <v>2.27</v>
+        <v>2.289</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -9285,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.649</v>
+        <v>0.658</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9408,150 +9408,150 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C57" t="n">
-        <v>87.459</v>
+        <v>87.553</v>
       </c>
       <c r="D57" t="n">
-        <v>22.432</v>
+        <v>22.395</v>
       </c>
       <c r="E57" t="n">
-        <v>39.919</v>
+        <v>39.947</v>
       </c>
       <c r="F57" t="n">
-        <v>8.919</v>
+        <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>25.757</v>
+        <v>25.711</v>
       </c>
       <c r="H57" t="n">
-        <v>15.838</v>
+        <v>15.763</v>
       </c>
       <c r="I57" t="n">
-        <v>21.216</v>
+        <v>21.263</v>
       </c>
       <c r="J57" t="n">
-        <v>20.27</v>
+        <v>20.263</v>
       </c>
       <c r="K57" t="n">
-        <v>24.595</v>
+        <v>24.684</v>
       </c>
       <c r="L57" t="n">
-        <v>13.351</v>
+        <v>13.342</v>
       </c>
       <c r="M57" t="n">
-        <v>6.162</v>
+        <v>6.105</v>
       </c>
       <c r="N57" t="n">
-        <v>4.919</v>
+        <v>4.947</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>14.081</v>
+        <v>13.947</v>
       </c>
       <c r="Q57" t="n">
-        <v>12.703</v>
+        <v>12.579</v>
       </c>
       <c r="R57" t="n">
-        <v>18.973</v>
+        <v>18.947</v>
       </c>
       <c r="S57" t="n">
-        <v>21.378</v>
+        <v>21.368</v>
       </c>
       <c r="T57" t="n">
-        <v>3899</v>
+        <v>4013</v>
       </c>
       <c r="U57" t="n">
-        <v>10.378</v>
+        <v>10.368</v>
       </c>
       <c r="V57" t="n">
-        <v>13.838</v>
+        <v>13.789</v>
       </c>
       <c r="W57" t="n">
-        <v>10.27</v>
+        <v>10.289</v>
       </c>
       <c r="X57" t="n">
-        <v>6.027</v>
+        <v>6</v>
       </c>
       <c r="Y57" t="n">
-        <v>29.432</v>
+        <v>29.263</v>
       </c>
       <c r="Z57" t="n">
-        <v>35.324</v>
+        <v>35.184</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.833</v>
+        <v>0.832</v>
       </c>
       <c r="AB57" t="n">
-        <v>8.026999999999999</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="AC57" t="n">
-        <v>17.865</v>
+        <v>17.974</v>
       </c>
       <c r="AD57" t="n">
         <v>0.449</v>
       </c>
       <c r="AE57" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.568</v>
+        <v>2.553</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.316</v>
+        <v>0.32</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.243</v>
+        <v>1.263</v>
       </c>
       <c r="AI57" t="n">
-        <v>3.135</v>
+        <v>3.184</v>
       </c>
       <c r="AJ57" t="n">
         <v>0.397</v>
       </c>
       <c r="AK57" t="n">
-        <v>7.676</v>
+        <v>7.737</v>
       </c>
       <c r="AL57" t="n">
-        <v>22.622</v>
+        <v>22.526</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.339</v>
+        <v>0.343</v>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>202:01</t>
+          <t>201:58</t>
         </is>
       </c>
       <c r="AO57" t="n">
-        <v>89.092</v>
+        <v>88.961</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.545</v>
+        <v>0.547</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.583</v>
+        <v>0.584</v>
       </c>
       <c r="AR57" t="n">
-        <v>0.982</v>
+        <v>0.984</v>
       </c>
       <c r="AS57" t="n">
-        <v>0.158</v>
+        <v>0.157</v>
       </c>
       <c r="AT57" t="n">
-        <v>0.241</v>
+        <v>0.24</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.44</v>
+        <v>1.453</v>
       </c>
       <c r="AV57" t="n">
-        <v>4.664</v>
+        <v>4.708</v>
       </c>
       <c r="AW57" t="n">
-        <v>6.104</v>
+        <v>6.16</v>
       </c>
       <c r="AX57" t="n">
         <v>0.2</v>
@@ -9560,7 +9560,7 @@
         <v>0.075</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0.139</v>
+        <v>0.14</v>
       </c>
       <c r="BA57" t="n">
         <v>0</v>
@@ -9573,156 +9573,156 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C58" t="n">
-        <v>86.351</v>
+        <v>86.211</v>
       </c>
       <c r="D58" t="n">
-        <v>20.081</v>
+        <v>20.053</v>
       </c>
       <c r="E58" t="n">
-        <v>35.324</v>
+        <v>35.289</v>
       </c>
       <c r="F58" t="n">
-        <v>10.027</v>
+        <v>10.026</v>
       </c>
       <c r="G58" t="n">
-        <v>28.459</v>
+        <v>28.474</v>
       </c>
       <c r="H58" t="n">
-        <v>16.108</v>
+        <v>16.026</v>
       </c>
       <c r="I58" t="n">
-        <v>21.108</v>
+        <v>21.079</v>
       </c>
       <c r="J58" t="n">
-        <v>19.27</v>
+        <v>19.184</v>
       </c>
       <c r="K58" t="n">
-        <v>22.108</v>
+        <v>22.158</v>
       </c>
       <c r="L58" t="n">
-        <v>10.757</v>
+        <v>10.684</v>
       </c>
       <c r="M58" t="n">
-        <v>8</v>
+        <v>7.974</v>
       </c>
       <c r="N58" t="n">
-        <v>4.919</v>
+        <v>4.947</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>13.216</v>
+        <v>13.053</v>
       </c>
       <c r="Q58" t="n">
-        <v>11.703</v>
+        <v>11.526</v>
       </c>
       <c r="R58" t="n">
-        <v>19.27</v>
+        <v>19.316</v>
       </c>
       <c r="S58" t="n">
-        <v>20.919</v>
+        <v>20.842</v>
       </c>
       <c r="T58" t="n">
-        <v>3743</v>
+        <v>3834</v>
       </c>
       <c r="U58" t="n">
-        <v>12.378</v>
+        <v>12.158</v>
       </c>
       <c r="V58" t="n">
-        <v>11.865</v>
+        <v>11.868</v>
       </c>
       <c r="W58" t="n">
-        <v>9.189</v>
+        <v>9.211</v>
       </c>
       <c r="X58" t="n">
-        <v>5.514</v>
+        <v>5.526</v>
       </c>
       <c r="Y58" t="n">
-        <v>29.162</v>
+        <v>29.053</v>
       </c>
       <c r="Z58" t="n">
-        <v>34.459</v>
+        <v>34.289</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.846</v>
+        <v>0.847</v>
       </c>
       <c r="AB58" t="n">
-        <v>5.865</v>
+        <v>5.816</v>
       </c>
       <c r="AC58" t="n">
-        <v>14.378</v>
+        <v>14.342</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.408</v>
+        <v>0.406</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.162</v>
+        <v>1.211</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.595</v>
+        <v>2.684</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.448</v>
+        <v>0.451</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.541</v>
+        <v>1.553</v>
       </c>
       <c r="AI58" t="n">
-        <v>3.486</v>
+        <v>3.553</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.442</v>
+        <v>0.437</v>
       </c>
       <c r="AK58" t="n">
-        <v>8.486000000000001</v>
+        <v>8.474</v>
       </c>
       <c r="AL58" t="n">
-        <v>24.973</v>
+        <v>24.921</v>
       </c>
       <c r="AM58" t="n">
         <v>0.34</v>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>202:01</t>
+          <t>201:58</t>
         </is>
       </c>
       <c r="AO58" t="n">
-        <v>86.288</v>
+        <v>86.09099999999999</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.551</v>
+        <v>0.55</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.591</v>
+        <v>0.59</v>
       </c>
       <c r="AR58" t="n">
         <v>1.001</v>
       </c>
       <c r="AS58" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="AT58" t="n">
-        <v>0.253</v>
+        <v>0.251</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.458</v>
+        <v>1.47</v>
       </c>
       <c r="AV58" t="n">
-        <v>4.826</v>
+        <v>4.885</v>
       </c>
       <c r="AW58" t="n">
-        <v>6.284</v>
+        <v>6.355</v>
       </c>
       <c r="AX58" t="n">
         <v>0.194</v>
       </c>
       <c r="AY58" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="AZ58" t="n">
         <v>0.125</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
@@ -683,13 +683,13 @@
         <v>478</v>
       </c>
       <c r="N2" t="n">
-        <v>1112</v>
+        <v>513</v>
       </c>
       <c r="O2" t="n">
-        <v>1337</v>
+        <v>738</v>
       </c>
       <c r="P2" t="n">
-        <v>0.535871743486974</v>
+        <v>0.2957915831663326</v>
       </c>
       <c r="Q2" t="n">
         <v>307</v>
@@ -710,25 +710,25 @@
         <v>0.03887775551102204</v>
       </c>
       <c r="W2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="X2" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.04849699398797595</v>
+        <v>0.05330661322645291</v>
       </c>
       <c r="Z2" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AA2" t="n">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3430861723446894</v>
+        <v>0.3382765531062124</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.831712789827973</v>
+        <v>0.6951219512195121</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4494875549048316</v>
@@ -737,13 +737,13 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3966942148760331</v>
+        <v>0.3909774436090225</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3434579439252337</v>
+        <v>0.3436018957345972</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.663425579655946</v>
+        <v>1.390243902439024</v>
       </c>
       <c r="AI2" t="n">
         <v>0.6391752577319587</v>
@@ -813,13 +813,13 @@
         <v>12.57894736842105</v>
       </c>
       <c r="N3" t="n">
-        <v>29.26315789473684</v>
+        <v>13.5</v>
       </c>
       <c r="O3" t="n">
-        <v>35.18421052631579</v>
+        <v>19.42105263157895</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5358717434869739</v>
+        <v>0.2957915831663326</v>
       </c>
       <c r="Q3" t="n">
         <v>8.078947368421053</v>
@@ -840,25 +840,25 @@
         <v>0.03887775551102204</v>
       </c>
       <c r="W3" t="n">
-        <v>1.263157894736842</v>
+        <v>1.368421052631579</v>
       </c>
       <c r="X3" t="n">
-        <v>3.184210526315789</v>
+        <v>3.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04849699398797595</v>
+        <v>0.0533066132264529</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.736842105263158</v>
+        <v>7.631578947368421</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.52631578947368</v>
+        <v>22.21052631578947</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3430861723446894</v>
+        <v>0.3382765531062124</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8317127898279731</v>
+        <v>0.6951219512195121</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4494875549048317</v>
@@ -867,13 +867,13 @@
         <v>0.3195876288659794</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3966942148760331</v>
+        <v>0.3909774436090226</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3434579439252336</v>
+        <v>0.3436018957345972</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.663425579655946</v>
+        <v>1.390243902439024</v>
       </c>
       <c r="AI3" t="n">
         <v>0.6391752577319587</v>
@@ -943,13 +943,13 @@
         <v>438</v>
       </c>
       <c r="N4" t="n">
-        <v>1104</v>
+        <v>495</v>
       </c>
       <c r="O4" t="n">
-        <v>1303</v>
+        <v>694</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5377631035905902</v>
+        <v>0.2864217911679736</v>
       </c>
       <c r="Q4" t="n">
         <v>221</v>
@@ -970,25 +970,25 @@
         <v>0.04209657449442839</v>
       </c>
       <c r="W4" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="X4" t="n">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05571605447791993</v>
+        <v>0.06685926537350392</v>
       </c>
       <c r="Z4" t="n">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="AA4" t="n">
-        <v>947</v>
+        <v>920</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3908378043747421</v>
+        <v>0.3796945934791581</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8472755180353031</v>
+        <v>0.7132564841498559</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4055045871559633</v>
@@ -997,13 +997,13 @@
         <v>0.4509803921568628</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4370370370370371</v>
+        <v>0.4135802469135803</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3400211193241816</v>
+        <v>0.3413043478260869</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.694551036070606</v>
+        <v>1.426512968299712</v>
       </c>
       <c r="AI4" t="n">
         <v>0.9019607843137255</v>
@@ -1073,13 +1073,13 @@
         <v>11.52631578947368</v>
       </c>
       <c r="N5" t="n">
-        <v>29.05263157894737</v>
+        <v>13.02631578947368</v>
       </c>
       <c r="O5" t="n">
-        <v>34.28947368421053</v>
+        <v>18.26315789473684</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5377631035905902</v>
+        <v>0.2864217911679736</v>
       </c>
       <c r="Q5" t="n">
         <v>5.815789473684211</v>
@@ -1100,25 +1100,25 @@
         <v>0.04209657449442839</v>
       </c>
       <c r="W5" t="n">
-        <v>1.552631578947368</v>
+        <v>1.763157894736842</v>
       </c>
       <c r="X5" t="n">
-        <v>3.552631578947369</v>
+        <v>4.263157894736842</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05571605447791993</v>
+        <v>0.06685926537350392</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.473684210526315</v>
+        <v>8.263157894736842</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.92105263157895</v>
+        <v>24.21052631578947</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3908378043747421</v>
+        <v>0.3796945934791581</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8472755180353032</v>
+        <v>0.713256484149856</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4055045871559633</v>
@@ -1127,13 +1127,13 @@
         <v>0.4509803921568628</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.437037037037037</v>
+        <v>0.4135802469135802</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3400211193241816</v>
+        <v>0.341304347826087</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.694551036070606</v>
+        <v>1.426512968299712</v>
       </c>
       <c r="AI5" t="n">
         <v>0.9019607843137255</v>
@@ -1498,13 +1498,13 @@
         <v>35</v>
       </c>
       <c r="Y8" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Z8" t="n">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.775</v>
+        <v>0.676</v>
       </c>
       <c r="AB8" t="n">
         <v>35</v>
@@ -1528,19 +1528,19 @@
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.3</v>
+        <v>0.273</v>
       </c>
       <c r="AK8" t="n">
         <v>61</v>
       </c>
       <c r="AL8" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.321</v>
+        <v>0.323</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.556</v>
+        <v>0.333</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>3</v>
       </c>
       <c r="Y10" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1855,22 +1855,22 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.3</v>
+        <v>0.222</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -2323,13 +2323,13 @@
         <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="Z13" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.784</v>
+        <v>0.609</v>
       </c>
       <c r="AB13" t="n">
         <v>42</v>
@@ -2488,13 +2488,13 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.846</v>
+        <v>0.778</v>
       </c>
       <c r="AB14" t="n">
         <v>2</v>
@@ -2515,22 +2515,22 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="AB15" t="n">
         <v>3</v>
@@ -2818,13 +2818,13 @@
         <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="Z16" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.767</v>
+        <v>0.575</v>
       </c>
       <c r="AB16" t="n">
         <v>18</v>
@@ -2848,19 +2848,19 @@
         <v>8</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.533</v>
+        <v>0.471</v>
       </c>
       <c r="AK16" t="n">
         <v>28</v>
       </c>
       <c r="AL16" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.378</v>
+        <v>0.389</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         <v>8</v>
       </c>
       <c r="Y17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Z17" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.593</v>
+        <v>0.421</v>
       </c>
       <c r="AB17" t="n">
         <v>8</v>
@@ -3013,19 +3013,19 @@
         <v>12</v>
       </c>
       <c r="AI17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.571</v>
+        <v>0.545</v>
       </c>
       <c r="AK17" t="n">
         <v>16</v>
       </c>
       <c r="AL17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -3148,13 +3148,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.895</v>
+        <v>0.8</v>
       </c>
       <c r="AB18" t="n">
         <v>7</v>
@@ -3478,13 +3478,13 @@
         <v>10</v>
       </c>
       <c r="Y20" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="Z20" t="n">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.873</v>
+        <v>0.786</v>
       </c>
       <c r="AB20" t="n">
         <v>42</v>
@@ -3973,13 +3973,13 @@
         <v>7</v>
       </c>
       <c r="Y23" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="Z23" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.871</v>
+        <v>0.771</v>
       </c>
       <c r="AB23" t="n">
         <v>20</v>
@@ -4138,13 +4138,13 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="Z24" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.805</v>
+        <v>0.75</v>
       </c>
       <c r="AB24" t="n">
         <v>8</v>
@@ -4303,13 +4303,13 @@
         <v>34</v>
       </c>
       <c r="Y25" t="n">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="Z25" t="n">
-        <v>209</v>
+        <v>105</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.866</v>
+        <v>0.733</v>
       </c>
       <c r="AB25" t="n">
         <v>54</v>
@@ -4333,19 +4333,19 @@
         <v>7</v>
       </c>
       <c r="AI25" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.368</v>
+        <v>0.304</v>
       </c>
       <c r="AK25" t="n">
         <v>54</v>
       </c>
       <c r="AL25" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
@@ -4468,13 +4468,13 @@
         <v>14</v>
       </c>
       <c r="Y26" t="n">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="Z26" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.887</v>
+        <v>0.774</v>
       </c>
       <c r="AB26" t="n">
         <v>24</v>
@@ -4495,22 +4495,22 @@
         <v>0.375</v>
       </c>
       <c r="AH26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.238</v>
+        <v>0.273</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.404</v>
+        <v>0.393</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -4798,13 +4798,13 @@
         <v>66</v>
       </c>
       <c r="Y28" t="n">
-        <v>237</v>
+        <v>91</v>
       </c>
       <c r="Z28" t="n">
-        <v>271</v>
+        <v>125</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.875</v>
+        <v>0.728</v>
       </c>
       <c r="AB28" t="n">
         <v>36</v>
@@ -4963,13 +4963,13 @@
         <v>7</v>
       </c>
       <c r="Y29" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.739</v>
+        <v>0.143</v>
       </c>
       <c r="AB29" t="n">
         <v>6</v>
@@ -4990,22 +4990,22 @@
         <v>0.333</v>
       </c>
       <c r="AH29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.196</v>
+        <v>0.18</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5293,13 +5293,13 @@
         <v>228</v>
       </c>
       <c r="Y31" t="n">
-        <v>1112</v>
+        <v>513</v>
       </c>
       <c r="Z31" t="n">
-        <v>1337</v>
+        <v>738</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.832</v>
+        <v>0.695</v>
       </c>
       <c r="AB31" t="n">
         <v>307</v>
@@ -5320,22 +5320,22 @@
         <v>0.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AI31" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.397</v>
+        <v>0.391</v>
       </c>
       <c r="AK31" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AL31" t="n">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -5458,13 +5458,13 @@
         <v>210</v>
       </c>
       <c r="Y32" t="n">
-        <v>1104</v>
+        <v>495</v>
       </c>
       <c r="Z32" t="n">
-        <v>1303</v>
+        <v>694</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.847</v>
+        <v>0.713</v>
       </c>
       <c r="AB32" t="n">
         <v>221</v>
@@ -5485,22 +5485,22 @@
         <v>0.451</v>
       </c>
       <c r="AH32" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="AI32" t="n">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.437</v>
+        <v>0.414</v>
       </c>
       <c r="AK32" t="n">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="n">
-        <v>947</v>
+        <v>920</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
@@ -5682,13 +5682,13 @@
         <v>0.921</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.263</v>
+        <v>1.974</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.211</v>
+        <v>2.921</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.775</v>
+        <v>0.676</v>
       </c>
       <c r="AB34" t="n">
         <v>0.921</v>
@@ -5712,19 +5712,19 @@
         <v>0.079</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.263</v>
+        <v>0.289</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.3</v>
+        <v>0.273</v>
       </c>
       <c r="AK34" t="n">
         <v>1.605</v>
       </c>
       <c r="AL34" t="n">
-        <v>5</v>
+        <v>4.974</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.321</v>
+        <v>0.323</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
@@ -5847,13 +5847,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.125</v>
+        <v>0.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.556</v>
+        <v>0.333</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -6012,13 +6012,13 @@
         <v>0.12</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.68</v>
+        <v>0.12</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -6039,22 +6039,22 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.3</v>
+        <v>0.222</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
@@ -6177,13 +6177,13 @@
         <v>0.167</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.167</v>
+        <v>0.083</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.417</v>
+        <v>0.333</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -6507,13 +6507,13 @@
         <v>0.774</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.161</v>
+        <v>1.355</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.032</v>
+        <v>2.226</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.784</v>
+        <v>0.609</v>
       </c>
       <c r="AB39" t="n">
         <v>1.355</v>
@@ -6672,13 +6672,13 @@
         <v>0.032</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.71</v>
+        <v>0.452</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.839</v>
+        <v>0.581</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.846</v>
+        <v>0.778</v>
       </c>
       <c r="AB40" t="n">
         <v>0.065</v>
@@ -6699,22 +6699,22 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.065</v>
+        <v>0.097</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.161</v>
+        <v>0.129</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.323</v>
+        <v>0.29</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
@@ -6837,13 +6837,13 @@
         <v>0.273</v>
       </c>
       <c r="Y41" t="n">
-        <v>1</v>
+        <v>0.545</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.364</v>
+        <v>0.909</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="AB41" t="n">
         <v>0.273</v>
@@ -7002,13 +7002,13 @@
         <v>0.211</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.474</v>
+        <v>0.605</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.921</v>
+        <v>1.053</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.767</v>
+        <v>0.575</v>
       </c>
       <c r="AB42" t="n">
         <v>0.474</v>
@@ -7032,19 +7032,19 @@
         <v>0.211</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.395</v>
+        <v>0.447</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.533</v>
+        <v>0.471</v>
       </c>
       <c r="AK42" t="n">
         <v>0.737</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.947</v>
+        <v>1.895</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.378</v>
+        <v>0.389</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
@@ -7167,13 +7167,13 @@
         <v>0.32</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.08</v>
+        <v>0.76</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.593</v>
+        <v>0.421</v>
       </c>
       <c r="AB43" t="n">
         <v>0.32</v>
@@ -7197,19 +7197,19 @@
         <v>0.48</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.571</v>
+        <v>0.545</v>
       </c>
       <c r="AK43" t="n">
         <v>0.64</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
@@ -7332,13 +7332,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.125</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.375</v>
+        <v>1.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.895</v>
+        <v>0.8</v>
       </c>
       <c r="AB44" t="n">
         <v>0.875</v>
@@ -7662,13 +7662,13 @@
         <v>0.303</v>
       </c>
       <c r="Y46" t="n">
-        <v>3.121</v>
+        <v>1.667</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.576</v>
+        <v>2.121</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.873</v>
+        <v>0.786</v>
       </c>
       <c r="AB46" t="n">
         <v>1.273</v>
@@ -8157,13 +8157,13 @@
         <v>0.233</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.467</v>
+        <v>1.233</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.833</v>
+        <v>1.6</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.871</v>
+        <v>0.771</v>
       </c>
       <c r="AB49" t="n">
         <v>0.667</v>
@@ -8322,13 +8322,13 @@
         <v>0.357</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.357</v>
+        <v>1.714</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.929</v>
+        <v>2.286</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.805</v>
+        <v>0.75</v>
       </c>
       <c r="AB50" t="n">
         <v>0.571</v>
@@ -8487,13 +8487,13 @@
         <v>1.03</v>
       </c>
       <c r="Y51" t="n">
-        <v>5.485</v>
+        <v>2.333</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.333</v>
+        <v>3.182</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.866</v>
+        <v>0.733</v>
       </c>
       <c r="AB51" t="n">
         <v>1.636</v>
@@ -8517,19 +8517,19 @@
         <v>0.212</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.576</v>
+        <v>0.697</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.368</v>
+        <v>0.304</v>
       </c>
       <c r="AK51" t="n">
         <v>1.636</v>
       </c>
       <c r="AL51" t="n">
-        <v>4.545</v>
+        <v>4.424</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
@@ -8652,13 +8652,13 @@
         <v>0.368</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.474</v>
+        <v>1.079</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.789</v>
+        <v>1.395</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.887</v>
+        <v>0.774</v>
       </c>
       <c r="AB52" t="n">
         <v>0.632</v>
@@ -8679,22 +8679,22 @@
         <v>0.375</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.132</v>
+        <v>0.158</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.553</v>
+        <v>0.579</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.238</v>
+        <v>0.273</v>
       </c>
       <c r="AK52" t="n">
-        <v>0.605</v>
+        <v>0.579</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.5</v>
+        <v>1.474</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.404</v>
+        <v>0.393</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
@@ -8982,13 +8982,13 @@
         <v>1.886</v>
       </c>
       <c r="Y54" t="n">
-        <v>6.771</v>
+        <v>2.6</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.743</v>
+        <v>3.571</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.875</v>
+        <v>0.728</v>
       </c>
       <c r="AB54" t="n">
         <v>1.029</v>
@@ -9147,13 +9147,13 @@
         <v>0.241</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.586</v>
+        <v>0.034</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.793</v>
+        <v>0.241</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.739</v>
+        <v>0.143</v>
       </c>
       <c r="AB55" t="n">
         <v>0.207</v>
@@ -9174,22 +9174,22 @@
         <v>0.333</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.034</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AK55" t="n">
-        <v>0.345</v>
+        <v>0.31</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.759</v>
+        <v>1.724</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.196</v>
+        <v>0.18</v>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
@@ -9477,13 +9477,13 @@
         <v>6</v>
       </c>
       <c r="Y57" t="n">
-        <v>29.263</v>
+        <v>13.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>35.184</v>
+        <v>19.421</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.832</v>
+        <v>0.695</v>
       </c>
       <c r="AB57" t="n">
         <v>8.079000000000001</v>
@@ -9504,22 +9504,22 @@
         <v>0.32</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.263</v>
+        <v>1.368</v>
       </c>
       <c r="AI57" t="n">
-        <v>3.184</v>
+        <v>3.5</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.397</v>
+        <v>0.391</v>
       </c>
       <c r="AK57" t="n">
-        <v>7.737</v>
+        <v>7.632</v>
       </c>
       <c r="AL57" t="n">
-        <v>22.526</v>
+        <v>22.211</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
@@ -9642,13 +9642,13 @@
         <v>5.526</v>
       </c>
       <c r="Y58" t="n">
-        <v>29.053</v>
+        <v>13.026</v>
       </c>
       <c r="Z58" t="n">
-        <v>34.289</v>
+        <v>18.263</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.847</v>
+        <v>0.713</v>
       </c>
       <c r="AB58" t="n">
         <v>5.816</v>
@@ -9669,22 +9669,22 @@
         <v>0.451</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.553</v>
+        <v>1.763</v>
       </c>
       <c r="AI58" t="n">
-        <v>3.553</v>
+        <v>4.263</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.437</v>
+        <v>0.414</v>
       </c>
       <c r="AK58" t="n">
-        <v>8.474</v>
+        <v>8.263</v>
       </c>
       <c r="AL58" t="n">
-        <v>24.921</v>
+        <v>24.211</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
